--- a/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
+++ b/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvonne.barkley\Github\BANTER_Pseudorca\manuscript\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jennifer.McCullough\Documents\GitHub\BANTER_Pseudorca\manuscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56478624-5149-466D-8CC5-9C1B683CE576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D31E3D9-FE4B-4021-928A-E151882EC3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19890" yWindow="1335" windowWidth="19080" windowHeight="12330" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3630" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SuppTable-TS1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="51">
   <si>
     <t>Survey Year</t>
   </si>
@@ -140,9 +140,6 @@
     <t>Cruise Number</t>
   </si>
   <si>
-    <t>MA1641; SE1642</t>
-  </si>
-  <si>
     <t>SE-11-08</t>
   </si>
   <si>
@@ -159,6 +156,42 @@
   </si>
   <si>
     <t xml:space="preserve">Total % Decrease to Pc  </t>
+  </si>
+  <si>
+    <t>SE-24-04</t>
+  </si>
+  <si>
+    <t>SE-23-03; LR-24-01</t>
+  </si>
+  <si>
+    <t>SE-21-02</t>
+  </si>
+  <si>
+    <t>SE-20-01</t>
+  </si>
+  <si>
+    <t>SE-19-01</t>
+  </si>
+  <si>
+    <t>SE-18-03</t>
+  </si>
+  <si>
+    <t>SE-17-06; LR-17-05</t>
+  </si>
+  <si>
+    <t>SE-16-04</t>
+  </si>
+  <si>
+    <t>SE-15-02</t>
+  </si>
+  <si>
+    <t>MA-1641; SE-1642</t>
+  </si>
+  <si>
+    <t>SE-12-03</t>
+  </si>
+  <si>
+    <t>SE-13-03</t>
   </si>
 </sst>
 </file>
@@ -381,14 +414,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -670,13 +703,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:K15"/>
-  <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="4" width="23.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="23.28515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
@@ -708,7 +741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="12">
         <v>2010</v>
       </c>
@@ -716,7 +749,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>11</v>
@@ -736,7 +769,7 @@
       </c>
       <c r="K3" s="14"/>
     </row>
-    <row r="4" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="12">
         <v>2011</v>
       </c>
@@ -744,7 +777,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>11</v>
@@ -762,14 +795,16 @@
       </c>
       <c r="K4" s="14"/>
     </row>
-    <row r="5" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="12">
         <v>2012</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="13"/>
+      <c r="D5" s="13" t="s">
+        <v>49</v>
+      </c>
       <c r="E5" s="14" t="s">
         <v>11</v>
       </c>
@@ -788,14 +823,16 @@
       </c>
       <c r="K5" s="14"/>
     </row>
-    <row r="6" spans="2:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12">
         <v>2013</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="13"/>
+      <c r="D6" s="13" t="s">
+        <v>50</v>
+      </c>
       <c r="E6" s="14" t="s">
         <v>12</v>
       </c>
@@ -814,14 +851,16 @@
       </c>
       <c r="K6" s="14"/>
     </row>
-    <row r="7" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="12">
         <v>2015</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="13"/>
+      <c r="D7" s="13" t="s">
+        <v>47</v>
+      </c>
       <c r="E7" s="14" t="s">
         <v>13</v>
       </c>
@@ -838,14 +877,16 @@
       </c>
       <c r="K7" s="14"/>
     </row>
-    <row r="8" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12">
         <v>2016</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="13"/>
+      <c r="D8" s="13" t="s">
+        <v>46</v>
+      </c>
       <c r="E8" s="14" t="s">
         <v>13</v>
       </c>
@@ -864,14 +905,16 @@
       </c>
       <c r="K8" s="14"/>
     </row>
-    <row r="9" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12">
         <v>2017</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="13"/>
+      <c r="D9" s="13" t="s">
+        <v>45</v>
+      </c>
       <c r="E9" s="14" t="s">
         <v>13</v>
       </c>
@@ -890,14 +933,16 @@
       </c>
       <c r="K9" s="14"/>
     </row>
-    <row r="10" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="12">
         <v>2018</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="13"/>
+      <c r="D10" s="13" t="s">
+        <v>44</v>
+      </c>
       <c r="E10" s="14" t="s">
         <v>13</v>
       </c>
@@ -914,14 +959,16 @@
       </c>
       <c r="K10" s="14"/>
     </row>
-    <row r="11" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="12">
         <v>2019</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="13"/>
+      <c r="D11" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="E11" s="14" t="s">
         <v>13</v>
       </c>
@@ -938,14 +985,16 @@
       </c>
       <c r="K11" s="14"/>
     </row>
-    <row r="12" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="12">
         <v>2020</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="13"/>
+      <c r="D12" s="13" t="s">
+        <v>42</v>
+      </c>
       <c r="E12" s="14" t="s">
         <v>13</v>
       </c>
@@ -962,14 +1011,16 @@
       </c>
       <c r="K12" s="14"/>
     </row>
-    <row r="13" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="12">
         <v>2021</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="13"/>
+      <c r="D13" s="13" t="s">
+        <v>41</v>
+      </c>
       <c r="E13" s="14" t="s">
         <v>13</v>
       </c>
@@ -986,14 +1037,16 @@
       </c>
       <c r="K13" s="14"/>
     </row>
-    <row r="14" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="12">
         <v>2023</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="13"/>
+      <c r="D14" s="13" t="s">
+        <v>40</v>
+      </c>
       <c r="E14" s="14" t="s">
         <v>13</v>
       </c>
@@ -1010,14 +1063,16 @@
       </c>
       <c r="K14" s="14"/>
     </row>
-    <row r="15" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="12">
         <v>2024</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="13"/>
+      <c r="D15" s="13" t="s">
+        <v>39</v>
+      </c>
       <c r="E15" s="14" t="s">
         <v>13</v>
       </c>
@@ -1043,64 +1098,64 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C3CA73-E650-4EB7-93C1-D459BAC41A38}">
   <dimension ref="B3:L20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" customWidth="1"/>
-    <col min="6" max="12" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="12" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="19" t="s">
+    <row r="3" spans="2:12" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="19" t="s">
+      <c r="F3" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="18" t="s">
         <v>30</v>
       </c>
       <c r="I3" s="16"/>
       <c r="J3" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="18">
+    <row r="4" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="17">
         <v>2017</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="17">
         <v>558</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="17">
         <v>448</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="17">
         <f t="shared" ref="E4:E9" si="0">ROUND((C4-D4)/C4, 2)</f>
         <v>0.2</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="17">
         <v>110</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="17">
         <f>ROUND((D4-F4)/D4, 2)</f>
         <v>0.75</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="17">
         <v>11</v>
       </c>
       <c r="J4">
@@ -1108,28 +1163,28 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="18">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="17">
         <v>2023</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="17">
         <v>388</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <v>321</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="17">
         <f t="shared" si="0"/>
         <v>0.17</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="17">
         <v>67</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="17">
         <f t="shared" ref="G5:G9" si="1">ROUND((D5-F5)/D5, 2)</f>
         <v>0.79</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="17">
         <v>9</v>
       </c>
       <c r="J5">
@@ -1137,28 +1192,28 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="20">
+    <row r="6" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="19">
         <v>2024</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="19">
         <v>122</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>87</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <f t="shared" si="0"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="19">
         <v>35</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="19">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="19">
         <v>0</v>
       </c>
       <c r="J6">
@@ -1166,10 +1221,10 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <f>SUM(C4:C6)</f>
@@ -1192,33 +1247,33 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12">
         <f>C9-D9</f>
         <v>212</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D18">
         <f>C4-F4</f>
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19">
         <f t="shared" ref="D19:D20" si="2">C5-F5</f>
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D20">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -1233,21 +1288,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC43C8DF-330E-4085-938E-0299F38AFB9F}">
   <dimension ref="B3:E13"/>
-  <sheetFormatPr defaultColWidth="21.5546875" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="21.5703125" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-    </row>
-    <row r="4" spans="2:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="2:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
       <c r="C4" s="7" t="s">
         <v>22</v>
@@ -1259,7 +1314,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
         <v>2017</v>
       </c>
@@ -1273,7 +1328,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="6">
         <v>2023</v>
       </c>
@@ -1287,7 +1342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="6">
         <v>2024</v>
       </c>
@@ -1301,37 +1356,37 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>

--- a/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
+++ b/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jennifer.McCullough\Documents\GitHub\BANTER_Pseudorca\manuscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D31E3D9-FE4B-4021-928A-E151882EC3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6CC7E0-0448-4CB9-A710-E09D139487D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3630" yWindow="-16320" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="SuppTable-TS1" sheetId="1" r:id="rId1"/>
-    <sheet name="Table1-Results" sheetId="3" r:id="rId2"/>
-    <sheet name="VVAO" sheetId="2" r:id="rId3"/>
+    <sheet name="Threshold_Table" sheetId="4" r:id="rId1"/>
+    <sheet name="SuppTable-TS1" sheetId="1" r:id="rId2"/>
+    <sheet name="TableX-Results" sheetId="3" r:id="rId3"/>
+    <sheet name="VVAO" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="122">
   <si>
     <t>Survey Year</t>
   </si>
@@ -192,13 +193,229 @@
   </si>
   <si>
     <t>SE-13-03</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Reduced</t>
+  </si>
+  <si>
+    <t>Pc</t>
+  </si>
+  <si>
+    <t>reduction per cruise</t>
+  </si>
+  <si>
+    <t>Removed from &lt;10</t>
+  </si>
+  <si>
+    <t>SSC</t>
+  </si>
+  <si>
+    <t>total removed</t>
+  </si>
+  <si>
+    <t>Overall reduction %</t>
+  </si>
+  <si>
+    <t>Average reduction %</t>
+  </si>
+  <si>
+    <t>Median reduction %</t>
+  </si>
+  <si>
+    <t>Jen Math :)</t>
+  </si>
+  <si>
+    <t>Suvery Year</t>
+  </si>
+  <si>
+    <t>(false +)</t>
+  </si>
+  <si>
+    <t>Banter Threshold</t>
+  </si>
+  <si>
+    <t>Raw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSC </t>
+  </si>
+  <si>
+    <t>SA&amp;SSC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raw </t>
+  </si>
+  <si>
+    <t>69 (36)</t>
+  </si>
+  <si>
+    <t>44 (11)</t>
+  </si>
+  <si>
+    <t>55 (25)</t>
+  </si>
+  <si>
+    <t>33 (0)</t>
+  </si>
+  <si>
+    <t>51 (37)</t>
+  </si>
+  <si>
+    <t>33 (19)</t>
+  </si>
+  <si>
+    <t>30 (18)</t>
+  </si>
+  <si>
+    <t>14 (0)</t>
+  </si>
+  <si>
+    <t>14 (4)</t>
+  </si>
+  <si>
+    <t>13 (3)</t>
+  </si>
+  <si>
+    <t>11 (1)</t>
+  </si>
+  <si>
+    <t>10 (0)</t>
+  </si>
+  <si>
+    <t>134 (77)</t>
+  </si>
+  <si>
+    <t>90 (33)</t>
+  </si>
+  <si>
+    <t>96 (44)</t>
+  </si>
+  <si>
+    <t>57 (0)</t>
+  </si>
+  <si>
+    <t>55 (22)</t>
+  </si>
+  <si>
+    <t>41 (8)</t>
+  </si>
+  <si>
+    <t>44 (14)</t>
+  </si>
+  <si>
+    <t>31 (21)</t>
+  </si>
+  <si>
+    <t>17 (7)</t>
+  </si>
+  <si>
+    <t>24 (14)</t>
+  </si>
+  <si>
+    <t>10 (1)</t>
+  </si>
+  <si>
+    <t>9 (0)</t>
+  </si>
+  <si>
+    <t>67 (15)</t>
+  </si>
+  <si>
+    <t>78 (29)</t>
+  </si>
+  <si>
+    <t>52 (0)</t>
+  </si>
+  <si>
+    <t>40 (11)</t>
+  </si>
+  <si>
+    <t>33 (4)</t>
+  </si>
+  <si>
+    <t>36 (7)</t>
+  </si>
+  <si>
+    <t>29 (0)</t>
+  </si>
+  <si>
+    <t>21 (13)</t>
+  </si>
+  <si>
+    <t>12 (4)</t>
+  </si>
+  <si>
+    <t>17 (9)</t>
+  </si>
+  <si>
+    <t>8 (0)</t>
+  </si>
+  <si>
+    <t>9 (1)</t>
+  </si>
+  <si>
+    <t>70 (25)</t>
+  </si>
+  <si>
+    <t>53 (8)</t>
+  </si>
+  <si>
+    <t>62 (17)</t>
+  </si>
+  <si>
+    <t>45 (0)</t>
+  </si>
+  <si>
+    <t>27 (2)</t>
+  </si>
+  <si>
+    <t>25 (0)</t>
+  </si>
+  <si>
+    <t>6 (2)</t>
+  </si>
+  <si>
+    <t>5 (1)</t>
+  </si>
+  <si>
+    <t>4 (0)</t>
+  </si>
+  <si>
+    <t>6 (0)</t>
+  </si>
+  <si>
+    <t>39 (4)</t>
+  </si>
+  <si>
+    <t>36 (1)</t>
+  </si>
+  <si>
+    <t>38 (3)</t>
+  </si>
+  <si>
+    <t>35 (0)</t>
+  </si>
+  <si>
+    <t>3 (0)</t>
+  </si>
+  <si>
+    <t>12 (0)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,6 +451,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -249,7 +474,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -370,11 +595,152 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -420,6 +786,66 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -701,6 +1127,399 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16B82A36-BAB4-4DA2-945D-9C525C938092}">
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" style="24" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" style="25" customWidth="1"/>
+    <col min="6" max="8" width="6.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="7.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="27"/>
+      <c r="B1" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="27">
+        <v>2017</v>
+      </c>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="27">
+        <v>2023</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="27">
+        <v>2024</v>
+      </c>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="36"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="40"/>
+      <c r="B3" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="M3" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="N3" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="O3" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="P3" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q3" s="31" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="41">
+        <v>0.5</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="M4" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="N4" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="O4" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="P4" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q4" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="41">
+        <v>0.6</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="J5" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="K5" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="L5" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="M5" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="N5" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="O5" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="P5" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q5" s="31" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="41">
+        <v>0.7</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="L6" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="M6" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="N6" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="O6" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="P6" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q6" s="31" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="41">
+        <v>0.8</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="J7" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="K7" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="L7" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="N7" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="O7" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="P7" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q7" s="31" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="42">
+        <v>0.9</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="K8" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="L8" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="M8" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="N8" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="O8" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="P8" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q8" s="34" t="s">
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:K15"/>
   <sheetFormatPr defaultColWidth="14.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1095,11 +1914,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C3CA73-E650-4EB7-93C1-D459BAC41A38}">
-  <dimension ref="B3:L20"/>
+  <dimension ref="A3:L31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" customWidth="1"/>
     <col min="5" max="5" width="10.42578125" customWidth="1"/>
@@ -1139,14 +1959,14 @@
         <v>2017</v>
       </c>
       <c r="C4" s="17">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D4" s="17">
         <v>448</v>
       </c>
       <c r="E4" s="17">
         <f t="shared" ref="E4:E9" si="0">ROUND((C4-D4)/C4, 2)</f>
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="F4" s="17">
         <v>110</v>
@@ -1162,6 +1982,10 @@
         <f>ROUND((C4-33)/C4,2)</f>
         <v>0.94</v>
       </c>
+      <c r="L4">
+        <f>C4-F4</f>
+        <v>445</v>
+      </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="17">
@@ -1191,6 +2015,10 @@
         <f>ROUND((C5-14)/C5,2)</f>
         <v>0.96</v>
       </c>
+      <c r="L5">
+        <f>C5-F5</f>
+        <v>321</v>
+      </c>
     </row>
     <row r="6" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="19">
@@ -1219,6 +2047,10 @@
       <c r="J6">
         <f>ROUND((C6-10)/C6,2)</f>
         <v>0.92</v>
+      </c>
+      <c r="L6">
+        <f>C6-F6</f>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
@@ -1228,7 +2060,7 @@
       </c>
       <c r="C9">
         <f>SUM(C4:C6)</f>
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="D9">
         <f>SUM(D4:D6)</f>
@@ -1253,7 +2085,7 @@
       </c>
       <c r="D12">
         <f>C9-D9</f>
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
@@ -1261,22 +2093,140 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D18">
-        <f>C4-F4</f>
-        <v>448</v>
-      </c>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>555</v>
+      </c>
+      <c r="C19">
+        <v>110</v>
+      </c>
       <c r="D19">
-        <f t="shared" ref="D19:D20" si="2">C5-F5</f>
-        <v>321</v>
-      </c>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="E19" s="21">
+        <f>(B19-C19)/B19</f>
+        <v>0.80180180180180183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>388</v>
+      </c>
+      <c r="C20">
+        <v>67</v>
+      </c>
       <c r="D20">
+        <v>14</v>
+      </c>
+      <c r="E20" s="21">
+        <f t="shared" ref="E20:E21" si="2">(B20-C20)/B20</f>
+        <v>0.82731958762886593</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>122</v>
+      </c>
+      <c r="C21">
+        <v>35</v>
+      </c>
+      <c r="D21">
+        <v>10</v>
+      </c>
+      <c r="E21" s="21">
         <f t="shared" si="2"/>
-        <v>87</v>
+        <v>0.71311475409836067</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="22">
+        <f>SUM(B19:B21)</f>
+        <v>1065</v>
+      </c>
+      <c r="C22" s="22">
+        <f>SUM(C19:C21)</f>
+        <v>212</v>
+      </c>
+      <c r="D22" s="22">
+        <f>SUM(D19:D21)</f>
+        <v>57</v>
+      </c>
+      <c r="E22" s="22"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24">
+        <f>1068-755</f>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25">
+        <f>755-212</f>
+        <v>543</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="22">
+        <f>B24+B25</f>
+        <v>856</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="23">
+        <f>B26/B22</f>
+        <v>0.8037558685446009</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="21">
+        <f>AVERAGE(E19:E21)</f>
+        <v>0.78074538117634285</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="21">
+        <f>MEDIAN(E19:E21)</f>
+        <v>0.80180180180180183</v>
       </c>
     </row>
   </sheetData>
@@ -1285,9 +2235,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC43C8DF-330E-4085-938E-0299F38AFB9F}">
-  <dimension ref="B3:E13"/>
+  <dimension ref="B3:G13"/>
   <sheetFormatPr defaultColWidth="21.5703125" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="1"/>
@@ -1297,12 +2247,12 @@
     <col min="5" max="5" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20"/>
     </row>
-    <row r="4" spans="2:5" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
       <c r="C4" s="7" t="s">
         <v>22</v>
@@ -1314,21 +2264,29 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
         <v>2017</v>
       </c>
       <c r="C5" s="8">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D5" s="8">
         <v>12</v>
       </c>
       <c r="E5" s="9">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <f>C5+D5+E5</f>
+        <v>555</v>
+      </c>
+      <c r="G5">
+        <f>D5+E5</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="6">
         <v>2023</v>
       </c>
@@ -1341,52 +2299,68 @@
       <c r="E6" s="10">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <f t="shared" ref="F6:F7" si="0">C6+D6+E6</f>
+        <v>388</v>
+      </c>
+      <c r="G6">
+        <f t="shared" ref="G6:G7" si="1">D6+E6</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="6">
         <v>2024</v>
       </c>
       <c r="C7" s="10">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D7" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="10">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>132</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="2:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>

--- a/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
+++ b/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jennifer.McCullough\Documents\GitHub\BANTER_Pseudorca\manuscript\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvonne.barkley\Github\BANTER_Pseudorca\manuscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6CC7E0-0448-4CB9-A710-E09D139487D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D9931E-3541-4DC1-BFF3-EEC28517D345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Threshold_Table" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="126">
   <si>
     <t>Survey Year</t>
   </si>
@@ -177,9 +177,6 @@
     <t>SE-18-03</t>
   </si>
   <si>
-    <t>SE-17-06; LR-17-05</t>
-  </si>
-  <si>
     <t>SE-16-04</t>
   </si>
   <si>
@@ -406,6 +403,21 @@
   </si>
   <si>
     <t>12 (0)</t>
+  </si>
+  <si>
+    <t>Visually-Verified Acoustic Pseudorca Events</t>
+  </si>
+  <si>
+    <t>Visually-Verified Acoustic Other Events</t>
+  </si>
+  <si>
+    <t>8; 1</t>
+  </si>
+  <si>
+    <t>LR-17-05; SE-17-06</t>
+  </si>
+  <si>
+    <t>10; 11</t>
   </si>
 </sst>
 </file>
@@ -460,7 +472,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -470,6 +482,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -740,7 +758,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -785,9 +803,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -846,6 +861,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1129,388 +1153,388 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16B82A36-BAB4-4DA2-945D-9C525C938092}">
   <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" style="24" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" style="25" customWidth="1"/>
-    <col min="6" max="8" width="6.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="7.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="1" width="16.33203125" style="23" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.88671875" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.88671875" style="24" customWidth="1"/>
+    <col min="6" max="8" width="6.88671875" style="24" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.88671875" style="24" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="5.88671875" style="24" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="7.88671875" style="24" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.88671875" style="24" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.88671875" style="24" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.109375" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27"/>
-      <c r="B1" s="37" t="s">
+    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="26"/>
+      <c r="B1" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="38" t="s">
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="36"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="B2" s="26">
+        <v>2017</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="26">
+        <v>2023</v>
+      </c>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="26">
+        <v>2024</v>
+      </c>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="35"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="39"/>
+      <c r="B3" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="27">
-        <v>2017</v>
-      </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="27">
-        <v>2023</v>
-      </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="27">
-        <v>2024</v>
-      </c>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="36"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="40"/>
-      <c r="B3" s="30" t="s">
+      <c r="C3" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="D3" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="E3" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="F3" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="G3" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="L3" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="N3" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="O3" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="P3" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="B4" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="I3" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="J3" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="K3" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="M3" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="N3" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="O3" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="P3" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q3" s="31" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="41">
-        <v>0.5</v>
-      </c>
-      <c r="B4" s="30" t="s">
+      <c r="C4" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D4" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="F4" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="G4" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="26" t="s">
+      <c r="I4" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="J4" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="K4" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="M4" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="31" t="s">
+      <c r="N4" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="N4" s="30" t="s">
+      <c r="O4" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="O4" s="26" t="s">
+      <c r="P4" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="P4" s="26" t="s">
+      <c r="Q4" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="Q4" s="31" t="s">
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="40">
+        <v>0.6</v>
+      </c>
+      <c r="B5" s="29" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="41">
-        <v>0.6</v>
-      </c>
-      <c r="B5" s="30" t="s">
+      <c r="C5" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="D5" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="E5" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="30" t="s">
+      <c r="G5" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="H5" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="I5" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="I5" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="J5" s="30" t="s">
+      <c r="K5" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="K5" s="26" t="s">
+      <c r="L5" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="N5" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="O5" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="L5" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="M5" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="N5" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="O5" s="26" t="s">
+      <c r="P5" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="P5" s="26" t="s">
+      <c r="Q5" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="Q5" s="31" t="s">
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="40">
+        <v>0.7</v>
+      </c>
+      <c r="B6" s="29" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="41">
-        <v>0.7</v>
-      </c>
-      <c r="B6" s="30" t="s">
+      <c r="C6" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="D6" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="E6" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="F6" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="G6" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="H6" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="H6" s="26" t="s">
+      <c r="I6" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="J6" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="K6" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="L6" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="M6" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="N6" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="K6" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="L6" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="M6" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="N6" s="30" t="s">
+      <c r="O6" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="O6" s="26" t="s">
+      <c r="P6" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="P6" s="26" t="s">
+      <c r="Q6" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="Q6" s="31" t="s">
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="40">
+        <v>0.8</v>
+      </c>
+      <c r="B7" s="29" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="41">
-        <v>0.8</v>
-      </c>
-      <c r="B7" s="30" t="s">
+      <c r="C7" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="D7" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="F7" s="30" t="s">
+      <c r="G7" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="H7" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="I7" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="H7" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="I7" s="31" t="s">
+      <c r="J7" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="K7" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="M7" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="N7" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="K7" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="L7" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="N7" s="30" t="s">
+      <c r="O7" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="O7" s="26" t="s">
+      <c r="P7" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="P7" s="26" t="s">
+      <c r="Q7" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="Q7" s="31" t="s">
+    </row>
+    <row r="8" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="41">
+        <v>0.9</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="31" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="42">
-        <v>0.9</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="32" t="s">
+      <c r="G8" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="K8" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="L8" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="M8" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="N8" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="O8" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="H8" s="33" t="s">
+      <c r="P8" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="Q8" s="33" t="s">
         <v>120</v>
-      </c>
-      <c r="J8" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="K8" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="L8" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="M8" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="O8" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="P8" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q8" s="34" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1521,14 +1545,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:K15"/>
-  <sheetFormatPr defaultColWidth="14.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:M15"/>
+  <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="4" width="23.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="23.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
@@ -1541,7 +1565,7 @@
       <c r="E2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="43" t="s">
         <v>3</v>
       </c>
       <c r="G2" s="12" t="s">
@@ -1557,10 +1581,16 @@
         <v>18</v>
       </c>
       <c r="K2" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="M2" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
         <v>2010</v>
       </c>
@@ -1568,7 +1598,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>11</v>
@@ -1586,9 +1616,13 @@
       <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="14"/>
-    </row>
-    <row r="4" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K3" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="14"/>
+    </row>
+    <row r="4" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="12">
         <v>2011</v>
       </c>
@@ -1612,9 +1646,13 @@
       <c r="J4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="14"/>
-    </row>
-    <row r="5" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="44">
+        <v>2</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="14"/>
+    </row>
+    <row r="5" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12">
         <v>2012</v>
       </c>
@@ -1622,7 +1660,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>11</v>
@@ -1640,9 +1678,13 @@
       <c r="J5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="14"/>
-    </row>
-    <row r="6" spans="2:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K5" s="44">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="14"/>
+    </row>
+    <row r="6" spans="2:13" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12">
         <v>2013</v>
       </c>
@@ -1650,7 +1692,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>12</v>
@@ -1668,9 +1710,13 @@
       <c r="J6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="14"/>
-    </row>
-    <row r="7" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K6" s="2">
+        <v>2</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="14"/>
+    </row>
+    <row r="7" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="12">
         <v>2015</v>
       </c>
@@ -1678,7 +1724,7 @@
         <v>7</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>13</v>
@@ -1694,9 +1740,13 @@
       <c r="J7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="14"/>
-    </row>
-    <row r="8" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K7" s="2">
+        <v>2</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="14"/>
+    </row>
+    <row r="8" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="12">
         <v>2016</v>
       </c>
@@ -1704,7 +1754,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>13</v>
@@ -1722,9 +1772,13 @@
       <c r="J8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K8" s="14"/>
-    </row>
-    <row r="9" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="14"/>
+    </row>
+    <row r="9" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="12">
         <v>2017</v>
       </c>
@@ -1732,7 +1786,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>13</v>
@@ -1750,9 +1804,13 @@
       <c r="J9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="14"/>
-    </row>
-    <row r="10" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K9" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="14"/>
+    </row>
+    <row r="10" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="12">
         <v>2018</v>
       </c>
@@ -1776,9 +1834,11 @@
       <c r="J10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="14"/>
-    </row>
-    <row r="11" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="14"/>
+    </row>
+    <row r="11" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="12">
         <v>2019</v>
       </c>
@@ -1802,9 +1862,11 @@
       <c r="J11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="14"/>
-    </row>
-    <row r="12" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="14"/>
+    </row>
+    <row r="12" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="12">
         <v>2020</v>
       </c>
@@ -1828,9 +1890,13 @@
       <c r="J12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="14"/>
-    </row>
-    <row r="13" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K12" s="2">
+        <v>4</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="14"/>
+    </row>
+    <row r="13" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="12">
         <v>2021</v>
       </c>
@@ -1854,9 +1920,13 @@
       <c r="J13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K13" s="14"/>
-    </row>
-    <row r="14" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K13" s="2">
+        <v>9</v>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="14"/>
+    </row>
+    <row r="14" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="12">
         <v>2023</v>
       </c>
@@ -1880,9 +1950,11 @@
       <c r="J14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K14" s="14"/>
-    </row>
-    <row r="15" spans="2:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="14"/>
+    </row>
+    <row r="15" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="12">
         <v>2024</v>
       </c>
@@ -1906,7 +1978,9 @@
       <c r="J15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K15" s="14"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1917,16 +1991,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C3CA73-E650-4EB7-93C1-D459BAC41A38}">
   <dimension ref="A3:L31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="12" width="10.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" customWidth="1"/>
+    <col min="6" max="12" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="18" t="s">
         <v>0</v>
       </c>
@@ -1954,7 +2028,7 @@
       </c>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B4" s="17">
         <v>2017</v>
       </c>
@@ -1987,7 +2061,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="17">
         <v>2023</v>
       </c>
@@ -2020,7 +2094,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="19">
         <v>2024</v>
       </c>
@@ -2053,8 +2127,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>36</v>
       </c>
@@ -2079,7 +2153,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>35</v>
       </c>
@@ -2088,31 +2162,31 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
         <v>51</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>52</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>53</v>
       </c>
-      <c r="E18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>555</v>
       </c>
@@ -2122,12 +2196,12 @@
       <c r="D19">
         <v>33</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <f>(B19-C19)/B19</f>
         <v>0.80180180180180183</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>388</v>
       </c>
@@ -2137,12 +2211,12 @@
       <c r="D20">
         <v>14</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="20">
         <f t="shared" ref="E20:E21" si="2">(B20-C20)/B20</f>
         <v>0.82731958762886593</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>122</v>
       </c>
@@ -2152,79 +2226,79 @@
       <c r="D21">
         <v>10</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="20">
         <f t="shared" si="2"/>
         <v>0.71311475409836067</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="22">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="21">
         <f>SUM(B19:B21)</f>
         <v>1065</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="21">
         <f>SUM(C19:C21)</f>
         <v>212</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="21">
         <f>SUM(D19:D21)</f>
         <v>57</v>
       </c>
-      <c r="E22" s="22"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E22" s="21"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B24">
         <f>1068-755</f>
         <v>313</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B25">
         <f>755-212</f>
         <v>543</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="22">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="21">
         <f>B24+B25</f>
         <v>856</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="23">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="22">
         <f>B26/B22</f>
         <v>0.8037558685446009</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="21">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="20">
         <f>AVERAGE(E19:E21)</f>
         <v>0.78074538117634285</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="21">
+        <v>59</v>
+      </c>
+      <c r="B31" s="20">
         <f>MEDIAN(E19:E21)</f>
         <v>0.80180180180180183</v>
       </c>
@@ -2238,21 +2312,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC43C8DF-330E-4085-938E-0299F38AFB9F}">
   <dimension ref="B3:G13"/>
-  <sheetFormatPr defaultColWidth="21.5703125" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.5546875" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-    </row>
-    <row r="4" spans="2:7" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+    </row>
+    <row r="4" spans="2:7" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
       <c r="C4" s="7" t="s">
         <v>22</v>
@@ -2264,7 +2338,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11">
         <v>2017</v>
       </c>
@@ -2286,7 +2360,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>2023</v>
       </c>
@@ -2308,7 +2382,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <v>2024</v>
       </c>
@@ -2330,37 +2404,37 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
     </row>
-    <row r="10" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>

--- a/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
+++ b/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvonne.barkley\Github\BANTER_Pseudorca\manuscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D9931E-3541-4DC1-BFF3-EEC28517D345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E8231D-35F1-4F35-9800-9E068DF56C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="888" yWindow="768" windowWidth="31656" windowHeight="13224" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Threshold_Table" sheetId="4" r:id="rId1"/>
@@ -228,9 +228,6 @@
     <t>Suvery Year</t>
   </si>
   <si>
-    <t>(false +)</t>
-  </si>
-  <si>
     <t>Banter Threshold</t>
   </si>
   <si>
@@ -243,9 +240,6 @@
     <t xml:space="preserve">SSC </t>
   </si>
   <si>
-    <t>SA&amp;SSC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Raw </t>
   </si>
   <si>
@@ -418,6 +412,12 @@
   </si>
   <si>
     <t>10; 11</t>
+  </si>
+  <si>
+    <t>(false positives)</t>
+  </si>
+  <si>
+    <t>SA &amp; SSC</t>
   </si>
 </sst>
 </file>
@@ -427,7 +427,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,8 +464,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
-      <sz val="11"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -492,7 +507,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -754,11 +769,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -812,65 +851,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1152,389 +1197,385 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16B82A36-BAB4-4DA2-945D-9C525C938092}">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="B1:R14"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" style="23" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.88671875" style="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" style="24" customWidth="1"/>
-    <col min="6" max="8" width="6.88671875" style="24" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.88671875" style="24" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="5.88671875" style="24" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="7.88671875" style="24" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.88671875" style="24" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.88671875" style="24" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.109375" style="24"/>
+    <col min="1" max="1" width="9.109375" style="24"/>
+    <col min="2" max="2" width="15.33203125" style="23" customWidth="1"/>
+    <col min="3" max="18" width="12.44140625" style="24" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26"/>
-      <c r="B1" s="36" t="s">
+    <row r="1" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="28"/>
+      <c r="C2" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="37" t="s">
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="34"/>
+    </row>
+    <row r="3" spans="2:18" ht="42" x14ac:dyDescent="0.4">
+      <c r="B3" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="35"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="C3" s="35">
+        <v>2017</v>
+      </c>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="35">
+        <v>2023</v>
+      </c>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="35">
+        <v>2024</v>
+      </c>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="34"/>
+    </row>
+    <row r="4" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B4" s="37"/>
+      <c r="C4" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="26">
-        <v>2017</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="26">
-        <v>2023</v>
-      </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="26">
-        <v>2024</v>
-      </c>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="35"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="39"/>
-      <c r="B3" s="29" t="s">
+      <c r="D4" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="E4" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="F4" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="H4" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="K4" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="M4" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="O4" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="P4" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q4" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="R4" s="40" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B5" s="41">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="D5" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="I3" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="L3" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="M3" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="N3" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="O3" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="P3" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q3" s="30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="40">
-        <v>0.5</v>
-      </c>
-      <c r="B4" s="29" t="s">
+      <c r="E5" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="F5" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="G5" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="H5" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="I5" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="J5" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="K5" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="L5" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="M5" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="25" t="s">
+      <c r="N5" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="25" t="s">
+      <c r="O5" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="M4" s="30" t="s">
+      <c r="P5" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="N4" s="29" t="s">
+      <c r="Q5" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="O4" s="25" t="s">
+      <c r="R5" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="P4" s="25" t="s">
+    </row>
+    <row r="6" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B6" s="41">
+        <v>0.6</v>
+      </c>
+      <c r="C6" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="Q4" s="30" t="s">
+      <c r="D6" s="39" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="40">
-        <v>0.6</v>
-      </c>
-      <c r="B5" s="29" t="s">
+      <c r="E6" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="F6" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="H6" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="29" t="s">
+      <c r="I6" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="J6" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="L6" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="I5" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="J5" s="29" t="s">
+      <c r="M6" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="N6" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="O6" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="P6" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="K5" s="25" t="s">
+      <c r="Q6" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="L5" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="M5" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="N5" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="O5" s="25" t="s">
+      <c r="R6" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="P5" s="25" t="s">
+    </row>
+    <row r="7" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B7" s="41">
+        <v>0.7</v>
+      </c>
+      <c r="C7" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="Q5" s="30" t="s">
+      <c r="D7" s="39" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="40">
-        <v>0.7</v>
-      </c>
-      <c r="B6" s="29" t="s">
+      <c r="E7" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="F7" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="G7" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="H7" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="I7" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="J7" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="K7" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="I6" s="30" t="s">
+      <c r="L7" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="M7" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="N7" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="O7" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="P7" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="K6" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="L6" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="M6" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="N6" s="29" t="s">
+      <c r="Q7" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="O6" s="25" t="s">
+      <c r="R7" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="P6" s="25" t="s">
+    </row>
+    <row r="8" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B8" s="41">
+        <v>0.8</v>
+      </c>
+      <c r="C8" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="Q6" s="30" t="s">
+      <c r="D8" s="39" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="40">
-        <v>0.8</v>
-      </c>
-      <c r="B7" s="29" t="s">
+      <c r="E8" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="G8" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="H8" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" s="30" t="s">
+      <c r="I8" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="J8" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="K8" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="L8" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="I7" s="30" t="s">
+      <c r="M8" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="N8" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="O8" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="P8" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="K7" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="L7" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="M7" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="N7" s="29" t="s">
+      <c r="Q8" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="R8" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="P7" s="25" t="s">
+    </row>
+    <row r="9" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="42">
+        <v>0.9</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="Q7" s="30" t="s">
+      <c r="H9" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="I9" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="J9" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="K9" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="L9" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="M9" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="N9" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="O9" s="43" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="41">
-        <v>0.9</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="G8" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="H8" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="I8" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="J8" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="K8" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="M8" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="N8" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="O8" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="P8" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q8" s="33" t="s">
-        <v>120</v>
+      <c r="P9" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q9" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="R9" s="45" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C14" s="24" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1565,7 +1606,7 @@
       <c r="E2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="F2" s="25" t="s">
         <v>3</v>
       </c>
       <c r="G2" s="12" t="s">
@@ -1581,10 +1622,10 @@
         <v>18</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M2" s="12" t="s">
         <v>4</v>
@@ -1616,8 +1657,8 @@
       <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="44" t="s">
-        <v>123</v>
+      <c r="K3" s="26" t="s">
+        <v>121</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="14"/>
@@ -1646,7 +1687,7 @@
       <c r="J4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="44">
+      <c r="K4" s="26">
         <v>2</v>
       </c>
       <c r="L4" s="2"/>
@@ -1678,7 +1719,7 @@
       <c r="J5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="26">
         <v>1</v>
       </c>
       <c r="L5" s="2"/>
@@ -1786,7 +1827,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>13</v>
@@ -1805,7 +1846,7 @@
         <v>19</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="14"/>
@@ -2322,9 +2363,9 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
     </row>
     <row r="4" spans="2:7" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>

--- a/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
+++ b/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvonne.barkley\Github\BANTER_Pseudorca\manuscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E8231D-35F1-4F35-9800-9E068DF56C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A33E58-30D1-43E4-8D29-ABDD14ED5008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="888" yWindow="768" windowWidth="31656" windowHeight="13224" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="4140" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Threshold_Table" sheetId="4" r:id="rId1"/>
@@ -39,8 +39,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Reviewer</author>
+  </authors>
+  <commentList>
+    <comment ref="O2" authorId="0" shapeId="0" xr:uid="{F3D028D6-C6F0-40AC-98AD-084147D6A7A6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Reviewer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+YB - Not including since it's so variable and hard to understand.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="128">
   <si>
     <t>Survey Year</t>
   </si>
@@ -54,9 +88,6 @@
     <t>Minimum &amp; Maximum Hydrophone Spacing</t>
   </si>
   <si>
-    <t>References for more details</t>
-  </si>
-  <si>
     <t>Hawaiian EEZ</t>
   </si>
   <si>
@@ -90,9 +121,6 @@
     <t>Hydrophone Flat Frequency Response</t>
   </si>
   <si>
-    <t>2-40 kHz</t>
-  </si>
-  <si>
     <t>2.02.7b</t>
   </si>
   <si>
@@ -117,12 +145,6 @@
     <t>Visually Verified Pc</t>
   </si>
   <si>
-    <t>Sampling Rate (kHz)</t>
-  </si>
-  <si>
-    <t>2–85 kHz</t>
-  </si>
-  <si>
     <t>Total Acoustic Hours</t>
   </si>
   <si>
@@ -418,6 +440,24 @@
   </si>
   <si>
     <t>SA &amp; SSC</t>
+  </si>
+  <si>
+    <t>References for more details about the survey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sampling Rate </t>
+  </si>
+  <si>
+    <t>192 kHz</t>
+  </si>
+  <si>
+    <t>500 kHz</t>
+  </si>
+  <si>
+    <t>2 - 40 kHz</t>
+  </si>
+  <si>
+    <t>2 – 85 kHz</t>
   </si>
 </sst>
 </file>
@@ -427,7 +467,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,6 +526,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -797,7 +856,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -854,68 +913,71 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1208,374 +1270,374 @@
   <sheetData>
     <row r="1" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="28"/>
-      <c r="C2" s="29" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="32"/>
+    </row>
+    <row r="3" spans="2:18" ht="42" x14ac:dyDescent="0.4">
+      <c r="B3" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="33">
+        <v>2017</v>
+      </c>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="33">
+        <v>2023</v>
+      </c>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="33">
+        <v>2024</v>
+      </c>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="32"/>
+      <c r="O3" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="32"/>
+    </row>
+    <row r="4" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B4" s="35"/>
+      <c r="C4" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="34"/>
-    </row>
-    <row r="3" spans="2:18" ht="42" x14ac:dyDescent="0.4">
-      <c r="B3" s="46" t="s">
+      <c r="F4" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="G4" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="35">
-        <v>2017</v>
-      </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="35">
-        <v>2023</v>
-      </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="35">
-        <v>2024</v>
-      </c>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="34"/>
-    </row>
-    <row r="4" spans="2:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="B4" s="37"/>
-      <c r="C4" s="38" t="s">
+      <c r="H4" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="L4" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="M4" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="N4" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="O4" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="P4" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q4" s="37" t="s">
+        <v>61</v>
+      </c>
+      <c r="R4" s="38" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B5" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D5" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E5" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="G4" s="38" t="s">
+      <c r="F5" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="I4" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="K4" s="38" t="s">
+      <c r="G5" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="N5" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="O5" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q5" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="R5" s="38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B6" s="39">
+        <v>0.6</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="38" t="s">
         <v>66</v>
       </c>
-      <c r="L4" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="M4" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="N4" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="O4" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="P4" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q4" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="R4" s="40" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="B5" s="41">
-        <v>0.5</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="G5" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="H5" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="I5" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="J5" s="40" t="s">
+      <c r="G6" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="I6" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="J6" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="K5" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="L5" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="M5" s="39" t="s">
+      <c r="K6" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="L6" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="M6" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="N6" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="O6" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="N5" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="O5" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="P5" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q5" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="R5" s="40" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="2:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="B6" s="41">
-        <v>0.6</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="39" t="s">
+      <c r="P6" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="I6" s="39" t="s">
+      <c r="Q6" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="J6" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="K6" s="38" t="s">
+      <c r="R6" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="L6" s="39" t="s">
+    </row>
+    <row r="7" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B7" s="39">
+        <v>0.7</v>
+      </c>
+      <c r="C7" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="M6" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="N6" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="O6" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="P6" s="39" t="s">
+      <c r="D7" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="Q6" s="39" t="s">
+      <c r="E7" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="R6" s="40" t="s">
+      <c r="F7" s="38" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="7" spans="2:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="B7" s="41">
-        <v>0.7</v>
-      </c>
-      <c r="C7" s="38" t="s">
+      <c r="G7" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="H7" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="I7" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="J7" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="K7" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="39" t="s">
+      <c r="L7" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="M7" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="N7" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="O7" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="I7" s="39" t="s">
+      <c r="P7" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="J7" s="40" t="s">
+      <c r="Q7" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="K7" s="38" t="s">
+      <c r="R7" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="L7" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="M7" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="N7" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="O7" s="38" t="s">
+    </row>
+    <row r="8" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B8" s="39">
+        <v>0.8</v>
+      </c>
+      <c r="C8" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="P7" s="39" t="s">
+      <c r="D8" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="Q7" s="39" t="s">
+      <c r="E8" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="R7" s="40" t="s">
+      <c r="H8" s="37" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="8" spans="2:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="B8" s="41">
-        <v>0.8</v>
-      </c>
-      <c r="C8" s="38" t="s">
+      <c r="I8" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="J8" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="K8" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="E8" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="F8" s="40" t="s">
+      <c r="L8" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="M8" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="N8" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="O8" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="H8" s="39" t="s">
+      <c r="P8" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="I8" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="J8" s="40" t="s">
+      <c r="Q8" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="K8" s="38" t="s">
+      <c r="R8" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="L8" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="M8" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="N8" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="O8" s="38" t="s">
+    </row>
+    <row r="9" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="40">
+        <v>0.9</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="P8" s="39" t="s">
+      <c r="H9" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="I9" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="J9" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="K9" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="L9" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="M9" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="N9" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="O9" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="Q8" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="R8" s="40" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="42">
-        <v>0.9</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="F9" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="G9" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="H9" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="I9" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="J9" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="K9" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="L9" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="M9" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="N9" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="O9" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="P9" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q9" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="R9" s="45" t="s">
-        <v>118</v>
+      <c r="P9" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q9" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="R9" s="43" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
       <c r="C14" s="24" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -1585,15 +1647,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:M15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:O15"/>
   <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="4" width="23.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:15" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
@@ -1601,431 +1665,435 @@
         <v>1</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="O2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12">
         <v>2010</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="14">
-        <v>192</v>
-      </c>
-      <c r="I3" s="14">
+        <v>43</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="46">
         <v>1445</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="14"/>
-    </row>
-    <row r="4" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="14"/>
+      <c r="O3" s="46"/>
+    </row>
+    <row r="4" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="12">
         <v>2011</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="14">
-        <v>192</v>
-      </c>
-      <c r="I4" s="14"/>
-      <c r="J4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="26">
+        <v>29</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="G4" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="H4" s="46">
+        <v>253</v>
+      </c>
+      <c r="I4" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="47">
         <v>2</v>
       </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="14"/>
-    </row>
-    <row r="5" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K4" s="2"/>
+      <c r="L4" s="14"/>
+      <c r="O4" s="46"/>
+    </row>
+    <row r="5" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12">
         <v>2012</v>
       </c>
       <c r="C5" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="14">
-        <v>192</v>
-      </c>
-      <c r="I5" s="14">
+      <c r="F5" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="G5" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="H5" s="46">
         <v>263</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="26">
+      <c r="I5" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="47">
         <v>1</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="14"/>
-    </row>
-    <row r="6" spans="2:13" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K5" s="2"/>
+      <c r="L5" s="14"/>
+      <c r="O5" s="46"/>
+    </row>
+    <row r="6" spans="2:15" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12">
         <v>2013</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="14">
-        <v>192</v>
-      </c>
-      <c r="I6" s="14">
+        <v>45</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="G6" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" s="46">
         <v>293</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="2">
+      <c r="I6" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="47">
         <v>2</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="14"/>
-    </row>
-    <row r="7" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="2"/>
+      <c r="L6" s="14"/>
+      <c r="O6" s="46"/>
+    </row>
+    <row r="7" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="12">
         <v>2015</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="14">
-        <v>500</v>
-      </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="2">
+        <v>42</v>
+      </c>
+      <c r="E7" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" s="46"/>
+      <c r="I7" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="47">
         <v>2</v>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="14"/>
-    </row>
-    <row r="8" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K7" s="2"/>
+      <c r="L7" s="14"/>
+      <c r="O7" s="46"/>
+    </row>
+    <row r="8" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="12">
         <v>2016</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="14">
-        <v>500</v>
-      </c>
-      <c r="I8" s="14">
+        <v>41</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H8" s="46">
         <v>350</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="2">
+      <c r="I8" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="47">
         <v>1</v>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="14"/>
-    </row>
-    <row r="9" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K8" s="2"/>
+      <c r="L8" s="14"/>
+      <c r="O8" s="46"/>
+    </row>
+    <row r="9" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="12">
         <v>2017</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="14">
-        <v>500</v>
-      </c>
-      <c r="I9" s="14">
+        <v>118</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="46">
         <v>1743</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="14"/>
-    </row>
-    <row r="10" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="14"/>
+      <c r="O9" s="46"/>
+    </row>
+    <row r="10" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="12">
         <v>2018</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="14">
-        <v>500</v>
-      </c>
-      <c r="I10" s="14"/>
-      <c r="J10" s="2" t="s">
-        <v>20</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E10" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H10" s="46"/>
+      <c r="I10" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="47"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="14"/>
-    </row>
-    <row r="11" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="14"/>
+      <c r="O10" s="46"/>
+    </row>
+    <row r="11" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="12">
         <v>2019</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="14">
-        <v>500</v>
-      </c>
-      <c r="I11" s="14"/>
-      <c r="J11" s="2" t="s">
-        <v>20</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="E11" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G11" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="46"/>
+      <c r="I11" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="47"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="14"/>
-    </row>
-    <row r="12" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="14"/>
+      <c r="O11" s="46"/>
+    </row>
+    <row r="12" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="12">
         <v>2020</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="14">
-        <v>500</v>
-      </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="2">
+        <v>38</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" s="46"/>
+      <c r="I12" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="47">
         <v>4</v>
       </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="14"/>
-    </row>
-    <row r="13" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="2"/>
+      <c r="L12" s="14"/>
+      <c r="O12" s="46"/>
+    </row>
+    <row r="13" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="12">
         <v>2021</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="14">
-        <v>500</v>
-      </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="2">
+        <v>37</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G13" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H13" s="46"/>
+      <c r="I13" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="47">
         <v>9</v>
       </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="14"/>
-    </row>
-    <row r="14" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="2"/>
+      <c r="L13" s="14"/>
+      <c r="O13" s="46"/>
+    </row>
+    <row r="14" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="12">
         <v>2023</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="14">
-        <v>500</v>
-      </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="2" t="s">
-        <v>21</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H14" s="46"/>
+      <c r="I14" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="47"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="14"/>
-    </row>
-    <row r="15" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L14" s="14"/>
+      <c r="O14" s="46"/>
+    </row>
+    <row r="15" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="12">
         <v>2024</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="14">
-        <v>500</v>
-      </c>
-      <c r="I15" s="14"/>
-      <c r="J15" s="2" t="s">
-        <v>21</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>125</v>
+      </c>
+      <c r="H15" s="46"/>
+      <c r="I15" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="47"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="O15" s="46"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2046,26 +2114,26 @@
         <v>0</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I3" s="16"/>
       <c r="J3" s="16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L3" s="15"/>
     </row>
@@ -2171,7 +2239,7 @@
     <row r="7" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <f>SUM(C4:C6)</f>
@@ -2196,7 +2264,7 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D12">
         <f>C9-D9</f>
@@ -2205,26 +2273,26 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -2274,7 +2342,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B22" s="21">
         <f>SUM(B19:B21)</f>
@@ -2292,7 +2360,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B24">
         <f>1068-755</f>
@@ -2301,7 +2369,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B25">
         <f>755-212</f>
@@ -2310,7 +2378,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B26" s="21">
         <f>B24+B25</f>
@@ -2319,7 +2387,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B28" s="22">
         <f>B26/B22</f>
@@ -2328,7 +2396,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="21" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B30" s="20">
         <f>AVERAGE(E19:E21)</f>
@@ -2337,7 +2405,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B31" s="20">
         <f>MEDIAN(E19:E21)</f>
@@ -2363,20 +2431,20 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
     </row>
     <row r="4" spans="2:7" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>
       <c r="C4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">

--- a/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
+++ b/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvonne.barkley\Github\BANTER_Pseudorca\manuscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A33E58-30D1-43E4-8D29-ABDD14ED5008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDA9BBB-A165-4AB8-8CEB-C8BF30F2BEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="4140" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Threshold_Table" sheetId="4" r:id="rId1"/>
@@ -145,9 +145,6 @@
     <t>Visually Verified Pc</t>
   </si>
   <si>
-    <t>Total Acoustic Hours</t>
-  </si>
-  <si>
     <t>Total Events</t>
   </si>
   <si>
@@ -458,6 +455,9 @@
   </si>
   <si>
     <t>2 – 85 kHz</t>
+  </si>
+  <si>
+    <t>Total Recording Hours</t>
   </si>
 </sst>
 </file>
@@ -970,14 +970,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1272,7 +1272,7 @@
     <row r="2" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="26"/>
       <c r="C2" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D2" s="28"/>
       <c r="E2" s="28"/>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="3" spans="2:18" ht="42" x14ac:dyDescent="0.4">
       <c r="B3" s="44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" s="33">
         <v>2017</v>
@@ -1313,7 +1313,7 @@
       <c r="M3" s="30"/>
       <c r="N3" s="32"/>
       <c r="O3" s="33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P3" s="30"/>
       <c r="Q3" s="30"/>
@@ -1322,52 +1322,52 @@
     <row r="4" spans="2:18" ht="21" x14ac:dyDescent="0.4">
       <c r="B4" s="35"/>
       <c r="C4" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="E4" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="F4" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="G4" s="36" t="s">
-        <v>62</v>
-      </c>
       <c r="H4" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="J4" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="K4" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="K4" s="36" t="s">
-        <v>62</v>
-      </c>
       <c r="L4" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="N4" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="O4" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="N4" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="O4" s="36" t="s">
-        <v>62</v>
-      </c>
       <c r="P4" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q4" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="Q4" s="37" t="s">
-        <v>61</v>
-      </c>
       <c r="R4" s="38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="2:18" ht="21" x14ac:dyDescent="0.4">
@@ -1375,52 +1375,52 @@
         <v>0.5</v>
       </c>
       <c r="C5" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="E5" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="F5" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="G5" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="H5" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="I5" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="J5" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="J5" s="38" t="s">
+      <c r="K5" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="K5" s="36" t="s">
+      <c r="L5" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="L5" s="37" t="s">
+      <c r="M5" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="N5" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="N5" s="38" t="s">
+      <c r="O5" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="O5" s="36" t="s">
+      <c r="P5" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="P5" s="37" t="s">
+      <c r="Q5" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="Q5" s="37" t="s">
+      <c r="R5" s="38" t="s">
         <v>77</v>
-      </c>
-      <c r="R5" s="38" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="21" x14ac:dyDescent="0.4">
@@ -1428,52 +1428,52 @@
         <v>0.6</v>
       </c>
       <c r="C6" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="E6" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="F6" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6" s="36" t="s">
+      <c r="H6" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="I6" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="I6" s="37" t="s">
+      <c r="J6" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="J6" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="K6" s="36" t="s">
+      <c r="L6" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="M6" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="N6" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="O6" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="P6" s="37" t="s">
         <v>86</v>
       </c>
-      <c r="M6" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="N6" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="O6" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="P6" s="37" t="s">
+      <c r="Q6" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="Q6" s="37" t="s">
+      <c r="R6" s="38" t="s">
         <v>88</v>
-      </c>
-      <c r="R6" s="38" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="7" spans="2:18" ht="21" x14ac:dyDescent="0.4">
@@ -1481,52 +1481,52 @@
         <v>0.7</v>
       </c>
       <c r="C7" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="E7" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="F7" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="G7" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="H7" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="I7" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="I7" s="37" t="s">
+      <c r="J7" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="J7" s="38" t="s">
+      <c r="K7" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="K7" s="36" t="s">
+      <c r="L7" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="M7" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="N7" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="O7" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="L7" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="M7" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="N7" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="O7" s="36" t="s">
+      <c r="P7" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="P7" s="37" t="s">
+      <c r="Q7" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="Q7" s="37" t="s">
+      <c r="R7" s="38" t="s">
         <v>101</v>
-      </c>
-      <c r="R7" s="38" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="8" spans="2:18" ht="21" x14ac:dyDescent="0.4">
@@ -1534,52 +1534,52 @@
         <v>0.8</v>
       </c>
       <c r="C8" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="E8" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="E8" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="G8" s="36" t="s">
+      <c r="H8" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="I8" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="J8" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="I8" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="J8" s="38" t="s">
+      <c r="K8" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="K8" s="36" t="s">
+      <c r="L8" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="M8" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="N8" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="O8" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="L8" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="M8" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="N8" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="O8" s="36" t="s">
+      <c r="P8" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="P8" s="37" t="s">
+      <c r="Q8" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="Q8" s="37" t="s">
+      <c r="R8" s="38" t="s">
         <v>111</v>
-      </c>
-      <c r="R8" s="38" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="9" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
@@ -1587,57 +1587,57 @@
         <v>0.9</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F9" s="43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G9" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="H9" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="I9" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="K9" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="L9" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="M9" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="N9" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="O9" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="H9" s="42" t="s">
+      <c r="P9" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="I9" s="42" t="s">
+      <c r="Q9" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="J9" s="43" t="s">
+      <c r="R9" s="43" t="s">
         <v>113</v>
-      </c>
-      <c r="K9" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="L9" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="M9" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="N9" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="O9" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="P9" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q9" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="R9" s="43" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
       <c r="C14" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1665,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>2</v>
@@ -1674,22 +1674,22 @@
         <v>14</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="I2" s="12" t="s">
         <v>16</v>
       </c>
       <c r="J2" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="K2" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="K2" s="12" t="s">
-        <v>116</v>
-      </c>
       <c r="L2" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O2" s="25" t="s">
         <v>3</v>
@@ -1703,29 +1703,29 @@
         <v>4</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="G3" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="H3" s="46">
+      <c r="F3" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" s="45">
         <v>1445</v>
       </c>
-      <c r="I3" s="47" t="s">
+      <c r="I3" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="47" t="s">
-        <v>117</v>
+      <c r="J3" s="46" t="s">
+        <v>116</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="14"/>
-      <c r="O3" s="46"/>
+      <c r="O3" s="45"/>
     </row>
     <row r="4" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="12">
@@ -1735,29 +1735,29 @@
         <v>8</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="G4" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="H4" s="46">
+      <c r="F4" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="G4" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="H4" s="45">
         <v>253</v>
       </c>
-      <c r="I4" s="47" t="s">
+      <c r="I4" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="47">
+      <c r="J4" s="46">
         <v>2</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="14"/>
-      <c r="O4" s="46"/>
+      <c r="O4" s="45"/>
     </row>
     <row r="5" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12">
@@ -1767,29 +1767,29 @@
         <v>9</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="G5" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="H5" s="46">
+      <c r="F5" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="H5" s="45">
         <v>263</v>
       </c>
-      <c r="I5" s="47" t="s">
+      <c r="I5" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="46">
         <v>1</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="14"/>
-      <c r="O5" s="46"/>
+      <c r="O5" s="45"/>
     </row>
     <row r="6" spans="2:15" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12">
@@ -1799,29 +1799,29 @@
         <v>13</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="G6" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="H6" s="46">
+      <c r="F6" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="H6" s="45">
         <v>293</v>
       </c>
-      <c r="I6" s="47" t="s">
+      <c r="I6" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="47">
+      <c r="J6" s="46">
         <v>2</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="14"/>
-      <c r="O6" s="46"/>
+      <c r="O6" s="45"/>
     </row>
     <row r="7" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="12">
@@ -1831,27 +1831,29 @@
         <v>6</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="46" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="G7" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="H7" s="46"/>
-      <c r="I7" s="47" t="s">
+      <c r="F7" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="45">
+        <v>306</v>
+      </c>
+      <c r="I7" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="47">
+      <c r="J7" s="46">
         <v>2</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="14"/>
-      <c r="O7" s="46"/>
+      <c r="O7" s="45"/>
     </row>
     <row r="8" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="12">
@@ -1861,29 +1863,29 @@
         <v>5</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="46" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="G8" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="46">
+      <c r="F8" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="45">
         <v>350</v>
       </c>
-      <c r="I8" s="47" t="s">
+      <c r="I8" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="47">
+      <c r="J8" s="46">
         <v>1</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="14"/>
-      <c r="O8" s="46"/>
+      <c r="O8" s="45"/>
     </row>
     <row r="9" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="12">
@@ -1893,29 +1895,29 @@
         <v>4</v>
       </c>
       <c r="D9" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="G9" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="45">
+        <v>1743</v>
+      </c>
+      <c r="I9" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="46" t="s">
         <v>118</v>
-      </c>
-      <c r="E9" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="G9" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="H9" s="46">
-        <v>1743</v>
-      </c>
-      <c r="I9" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="47" t="s">
-        <v>119</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="14"/>
-      <c r="O9" s="46"/>
+      <c r="O9" s="45"/>
     </row>
     <row r="10" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="12">
@@ -1925,25 +1927,29 @@
         <v>6</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="G10" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="H10" s="46"/>
-      <c r="I10" s="47" t="s">
+      <c r="F10" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" s="45">
+        <v>339</v>
+      </c>
+      <c r="I10" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="47"/>
+      <c r="J10" s="46">
+        <v>0</v>
+      </c>
       <c r="K10" s="2"/>
       <c r="L10" s="14"/>
-      <c r="O10" s="46"/>
+      <c r="O10" s="45"/>
     </row>
     <row r="11" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="12">
@@ -1953,25 +1959,29 @@
         <v>5</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="46" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="G11" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="H11" s="46"/>
-      <c r="I11" s="47" t="s">
+      <c r="F11" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H11" s="45">
+        <v>109</v>
+      </c>
+      <c r="I11" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="47"/>
+      <c r="J11" s="46">
+        <v>2</v>
+      </c>
       <c r="K11" s="2"/>
       <c r="L11" s="14"/>
-      <c r="O11" s="46"/>
+      <c r="O11" s="45"/>
     </row>
     <row r="12" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="12">
@@ -1981,27 +1991,27 @@
         <v>5</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="G12" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="H12" s="46"/>
-      <c r="I12" s="47" t="s">
+      <c r="F12" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H12" s="45"/>
+      <c r="I12" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="47">
+      <c r="J12" s="46">
         <v>4</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="14"/>
-      <c r="O12" s="46"/>
+      <c r="O12" s="45"/>
     </row>
     <row r="13" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="12">
@@ -2011,27 +2021,27 @@
         <v>6</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="G13" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="H13" s="46"/>
-      <c r="I13" s="47" t="s">
+      <c r="F13" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H13" s="45"/>
+      <c r="I13" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="47">
-        <v>9</v>
+      <c r="J13" s="46">
+        <v>11</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="14"/>
-      <c r="O13" s="46"/>
+      <c r="O13" s="45"/>
     </row>
     <row r="14" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="12">
@@ -2041,25 +2051,27 @@
         <v>4</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="G14" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="H14" s="46"/>
-      <c r="I14" s="47" t="s">
+      <c r="F14" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="G14" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H14" s="45"/>
+      <c r="I14" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="47"/>
+      <c r="J14" s="46">
+        <v>5</v>
+      </c>
       <c r="K14" s="2"/>
       <c r="L14" s="14"/>
-      <c r="O14" s="46"/>
+      <c r="O14" s="45"/>
     </row>
     <row r="15" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="12">
@@ -2069,25 +2081,27 @@
         <v>7</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="G15" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="H15" s="46"/>
-      <c r="I15" s="47" t="s">
+      <c r="F15" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="H15" s="45"/>
+      <c r="I15" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="47"/>
+      <c r="J15" s="46">
+        <v>4</v>
+      </c>
       <c r="K15" s="2"/>
       <c r="L15" s="14"/>
-      <c r="O15" s="46"/>
+      <c r="O15" s="45"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -2114,26 +2128,26 @@
         <v>0</v>
       </c>
       <c r="C3" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="E3" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="18" t="s">
         <v>25</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>26</v>
       </c>
       <c r="I3" s="16"/>
       <c r="J3" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L3" s="15"/>
     </row>
@@ -2239,7 +2253,7 @@
     <row r="7" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <f>SUM(C4:C6)</f>
@@ -2264,7 +2278,7 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12">
         <f>C9-D9</f>
@@ -2273,26 +2287,26 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" t="s">
         <v>46</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>47</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>48</v>
-      </c>
-      <c r="E18" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -2342,7 +2356,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B22" s="21">
         <f>SUM(B19:B21)</f>
@@ -2360,7 +2374,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B24">
         <f>1068-755</f>
@@ -2369,7 +2383,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25">
         <f>755-212</f>
@@ -2378,7 +2392,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" s="21">
         <f>B24+B25</f>
@@ -2387,7 +2401,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B28" s="22">
         <f>B26/B22</f>
@@ -2396,7 +2410,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B30" s="20">
         <f>AVERAGE(E19:E21)</f>
@@ -2405,7 +2419,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B31" s="20">
         <f>MEDIAN(E19:E21)</f>
@@ -2431,9 +2445,9 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
     </row>
     <row r="4" spans="2:7" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4"/>

--- a/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
+++ b/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvonne.barkley\Github\BANTER_Pseudorca\manuscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDA9BBB-A165-4AB8-8CEB-C8BF30F2BEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422453C3-F1C3-4191-A16E-F118B3234197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44220" yWindow="5820" windowWidth="17280" windowHeight="10695" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Threshold_Table" sheetId="4" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="126">
   <si>
     <t>Survey Year</t>
   </si>
@@ -97,9 +97,6 @@
     <t>Marianas Archipelago</t>
   </si>
   <si>
-    <t>SE of Hawaiian EEZ</t>
-  </si>
-  <si>
     <t>Oahu to Palmyra</t>
   </si>
   <si>
@@ -160,9 +157,6 @@
     <t>Cruise Number</t>
   </si>
   <si>
-    <t>SE-11-08</t>
-  </si>
-  <si>
     <t>Events to Classify after SSC</t>
   </si>
   <si>
@@ -178,39 +172,6 @@
     <t xml:space="preserve">Total % Decrease to Pc  </t>
   </si>
   <si>
-    <t>SE-24-04</t>
-  </si>
-  <si>
-    <t>SE-23-03; LR-24-01</t>
-  </si>
-  <si>
-    <t>SE-21-02</t>
-  </si>
-  <si>
-    <t>SE-20-01</t>
-  </si>
-  <si>
-    <t>SE-19-01</t>
-  </si>
-  <si>
-    <t>SE-18-03</t>
-  </si>
-  <si>
-    <t>SE-16-04</t>
-  </si>
-  <si>
-    <t>SE-15-02</t>
-  </si>
-  <si>
-    <t>MA-1641; SE-1642</t>
-  </si>
-  <si>
-    <t>SE-12-03</t>
-  </si>
-  <si>
-    <t>SE-13-03</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -421,15 +382,9 @@
     <t>Visually-Verified Acoustic Pseudorca Events</t>
   </si>
   <si>
-    <t>Visually-Verified Acoustic Other Events</t>
-  </si>
-  <si>
     <t>8; 1</t>
   </si>
   <si>
-    <t>LR-17-05; SE-17-06</t>
-  </si>
-  <si>
     <t>10; 11</t>
   </si>
   <si>
@@ -439,9 +394,6 @@
     <t>SA &amp; SSC</t>
   </si>
   <si>
-    <t>References for more details about the survey</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sampling Rate </t>
   </si>
   <si>
@@ -458,6 +410,88 @@
   </si>
   <si>
     <t>Total Recording Hours</t>
+  </si>
+  <si>
+    <t>Southeast of Hawaiian EEZ</t>
+  </si>
+  <si>
+    <t>1641; 1642</t>
+  </si>
+  <si>
+    <t>1705; 1706</t>
+  </si>
+  <si>
+    <t>2303; 2401</t>
+  </si>
+  <si>
+    <t>Total Encounters for Sensitivity Analysis</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Should sum to 270</t>
+  </si>
+  <si>
+    <t>Bradford, A. L., Oleson, E. M., Forney, K. A., Moore, J. E., &amp; Barlow, J. (2021). Line-transect abundance estimates of cetaceans in US waters around the Hawaiian Islands in 2002, 2010, and 2017. NOAA Technical Memorandum NMFS-PIFSC-115</t>
+  </si>
+  <si>
+    <t>Yano, K. M., Oleson, E. M., McCullough, J. L., Hill, M. C., &amp; Henry, A. E. (2020). Cetacean and seabird data collected during the Winter Hawaiian Islands Cetacean and Ecosystem Assessment Survey (Winter HICEAS), January–March 2020. NOAA Technical Memorandum NMFS-PIFSC-111</t>
+  </si>
+  <si>
+    <t>References for further survey information</t>
+  </si>
+  <si>
+    <r>
+      <t>Barkley, Y., Oleson, E. M., Oswald, J. N., &amp; Franklin, E. C. (2019). Whistle classification of sympatric false killer whale populations in Hawaiian waters yields low accuracy rates. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Frontiers in Marine Science</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, 645.</t>
+    </r>
+  </si>
+  <si>
+    <t>Yano, K. M., Oleson, E. M., McCullough, J. L., Hill, M. C., Bradford, A. L., Joyce, T. W., ... &amp; Henry, A. E. (2025). Cetacean and Seabird Data Collected During the Hawaiian Islands Cetacean and Ecosystem Assessment Survey (HICEAS), July–December 2023.  NOAA Technical Memorandum NMFS-PIFSC-175</t>
+  </si>
+  <si>
+    <t>Yano, K. M., Hill, M. C., Oleson, E. M., McCullough, J. L., &amp; Henry, A. E. (2022). Cetacean and Seabird Data Collected During the Mariana Archipelago Cetacean Survey (MACS), May–July 2021.  NOAA Technical Memorandum NMFS-PIFSC-128</t>
+  </si>
+  <si>
+    <t>Yano, K. M., Oleson, E. M., Keating, J. L., Ballance, L. T., Hill, M. C., Bradford, A. L., Allen, A. N., Joyce, T. W., Moore, J. E., &amp; Henry, A. E. (2018). Cetacean and Seabird Data Collected during the Hawaiian Islands Cetacean and Ecosystem Assessment Survey (HICEAS), July—December 2017. NOAA Technical Memorandum NMFS-PIFSC-72</t>
   </si>
 </sst>
 </file>
@@ -467,7 +501,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -545,6 +579,25 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -856,12 +909,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -975,6 +1027,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1262,382 +1320,382 @@
   <dimension ref="B1:R14"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="24"/>
-    <col min="2" max="2" width="15.33203125" style="23" customWidth="1"/>
-    <col min="3" max="18" width="12.44140625" style="24" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="24"/>
+    <col min="1" max="1" width="9.109375" style="23"/>
+    <col min="2" max="2" width="15.33203125" style="22" customWidth="1"/>
+    <col min="3" max="18" width="12.44140625" style="23" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="26"/>
-      <c r="C2" s="27" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="31"/>
+    </row>
+    <row r="3" spans="2:18" ht="42" x14ac:dyDescent="0.4">
+      <c r="B3" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="32">
+        <v>2017</v>
+      </c>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="32">
+        <v>2023</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="32">
+        <v>2024</v>
+      </c>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="31"/>
+    </row>
+    <row r="4" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B4" s="34"/>
+      <c r="C4" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="O4" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="P4" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q4" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="R4" s="37" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B5" s="38">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="32"/>
-    </row>
-    <row r="3" spans="2:18" ht="42" x14ac:dyDescent="0.4">
-      <c r="B3" s="44" t="s">
+      <c r="K5" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="33">
-        <v>2017</v>
-      </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="33">
-        <v>2023</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="33">
-        <v>2024</v>
-      </c>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="32"/>
-    </row>
-    <row r="4" spans="2:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="B4" s="35"/>
-      <c r="C4" s="36" t="s">
+      <c r="L5" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="M5" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="N5" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="G4" s="36" t="s">
+      <c r="O5" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" s="37" t="s">
+      <c r="P5" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q5" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="R5" s="37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B6" s="38">
+        <v>0.6</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="J4" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="K4" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="L4" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="M4" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="N4" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="O4" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="P4" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q4" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="R4" s="38" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="B5" s="39">
-        <v>0.5</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="37" t="s">
+      <c r="K6" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="L6" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="N6" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="O6" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="J5" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="K5" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="L5" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="M5" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="N5" s="38" t="s">
+      <c r="P6" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="O5" s="36" t="s">
+      <c r="Q6" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="P5" s="37" t="s">
+      <c r="R6" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="Q5" s="37" t="s">
+    </row>
+    <row r="7" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B7" s="38">
+        <v>0.7</v>
+      </c>
+      <c r="C7" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="R5" s="38" t="s">
+      <c r="D7" s="36" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="6" spans="2:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="B6" s="39">
-        <v>0.6</v>
-      </c>
-      <c r="C6" s="36" t="s">
+      <c r="E7" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="F7" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="G7" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6" s="36" t="s">
+      <c r="H7" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="I7" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="37" t="s">
+      <c r="J7" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="36" t="s">
+      <c r="K7" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="L7" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="M7" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="N7" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="O7" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="M6" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="N6" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="O6" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="P6" s="37" t="s">
+      <c r="P7" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="Q6" s="37" t="s">
+      <c r="Q7" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="R6" s="38" t="s">
+      <c r="R7" s="37" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="B7" s="39">
-        <v>0.7</v>
-      </c>
-      <c r="C7" s="36" t="s">
+    <row r="8" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B8" s="38">
+        <v>0.8</v>
+      </c>
+      <c r="C8" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D8" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E8" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="G8" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="H8" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="I8" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="J8" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="K8" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="I7" s="37" t="s">
+      <c r="L8" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="M8" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="N8" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="O8" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="J7" s="38" t="s">
+      <c r="P8" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="K7" s="36" t="s">
+      <c r="Q8" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="L7" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="M7" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="N7" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="O7" s="36" t="s">
+      <c r="R8" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="P7" s="37" t="s">
+    </row>
+    <row r="9" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="39">
+        <v>0.9</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="Q7" s="37" t="s">
+      <c r="H9" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="J9" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="K9" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="M9" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="N9" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="O9" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="R7" s="38" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="2:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="B8" s="39">
-        <v>0.8</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="G8" s="36" t="s">
+      <c r="P9" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="R9" s="42" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C14" s="23" t="s">
         <v>104</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="I8" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="J8" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="K8" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="L8" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="M8" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="N8" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="O8" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="P8" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q8" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="R8" s="38" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="40">
-        <v>0.9</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="F9" s="43" t="s">
-        <v>107</v>
-      </c>
-      <c r="G9" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="H9" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="I9" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="K9" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="L9" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="M9" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="N9" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="O9" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="P9" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q9" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="R9" s="43" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="C14" s="24" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1648,460 +1706,511 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:O15"/>
+  <dimension ref="B2:O18"/>
   <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.21875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="23.6640625" customWidth="1"/>
+    <col min="12" max="12" width="35.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:15" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="O2" s="24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="B3" s="11">
+        <v>2010</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="H3" s="44">
+        <v>1445</v>
+      </c>
+      <c r="I3" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="O3" s="44"/>
+    </row>
+    <row r="4" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="11">
+        <v>2011</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="44">
+        <v>1108</v>
+      </c>
+      <c r="E4" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="H4" s="44">
+        <v>253</v>
+      </c>
+      <c r="I4" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="45">
+        <v>2</v>
+      </c>
+      <c r="K4" s="45">
+        <v>2</v>
+      </c>
+      <c r="L4" s="13"/>
+      <c r="O4" s="44"/>
+    </row>
+    <row r="5" spans="2:15" ht="52.2" x14ac:dyDescent="0.3">
+      <c r="B5" s="11">
+        <v>2012</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="44">
+        <v>1203</v>
+      </c>
+      <c r="E5" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="H5" s="44">
+        <v>263</v>
+      </c>
+      <c r="I5" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="45">
+        <v>1</v>
+      </c>
+      <c r="K5" s="45">
+        <v>1</v>
+      </c>
+      <c r="L5" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="O5" s="44"/>
+    </row>
+    <row r="6" spans="2:15" ht="52.2" x14ac:dyDescent="0.3">
+      <c r="B6" s="11">
+        <v>2013</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="44">
+        <v>1303</v>
+      </c>
+      <c r="E6" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6" s="44">
+        <v>293</v>
+      </c>
+      <c r="I6" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="45">
+        <v>2</v>
+      </c>
+      <c r="K6" s="45">
+        <v>2</v>
+      </c>
+      <c r="L6" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="O6" s="44"/>
+    </row>
+    <row r="7" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="11">
+        <v>2015</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="44">
+        <v>1502</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="H7" s="44">
+        <v>306</v>
+      </c>
+      <c r="I7" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="45">
+        <v>2</v>
+      </c>
+      <c r="K7" s="45">
+        <v>2</v>
+      </c>
+      <c r="L7" s="13"/>
+      <c r="O7" s="44"/>
+    </row>
+    <row r="8" spans="2:15" ht="52.2" x14ac:dyDescent="0.3">
+      <c r="B8" s="11">
+        <v>2016</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="44">
+        <v>1604</v>
+      </c>
+      <c r="E8" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="44">
+        <v>350</v>
+      </c>
+      <c r="I8" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="45">
+        <v>1</v>
+      </c>
+      <c r="K8" s="45">
+        <v>1</v>
+      </c>
+      <c r="L8" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="O8" s="44"/>
+    </row>
+    <row r="9" spans="2:15" ht="109.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="11">
+        <v>2017</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="44">
+        <v>1743</v>
+      </c>
+      <c r="I9" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="K9" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="L9" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="O9" s="44"/>
+    </row>
+    <row r="10" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="11">
+        <v>2018</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="44">
+        <v>1803</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="H10" s="44">
+        <v>339</v>
+      </c>
+      <c r="I10" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="45">
         <v>27</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="K10" s="45">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13"/>
+      <c r="O10" s="44"/>
+    </row>
+    <row r="11" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="11">
+        <v>2019</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="44">
+        <v>1901</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" s="44">
+        <v>109</v>
+      </c>
+      <c r="I11" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="45">
+        <v>10</v>
+      </c>
+      <c r="K11" s="45">
         <v>2</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="H2" s="12" t="s">
+      <c r="L11" s="13"/>
+      <c r="O11" s="44"/>
+    </row>
+    <row r="12" spans="2:15" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="11">
+        <v>2020</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="44">
+        <v>2001</v>
+      </c>
+      <c r="E12" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="44">
+        <v>475</v>
+      </c>
+      <c r="I12" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="45">
         <v>127</v>
       </c>
-      <c r="I2" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="K2" s="12" t="s">
+      <c r="K12" s="45">
+        <v>4</v>
+      </c>
+      <c r="L12" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="O12" s="44"/>
+    </row>
+    <row r="13" spans="2:15" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="B13" s="11">
+        <v>2021</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="44">
+        <v>2102</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="H13" s="44">
+        <v>339</v>
+      </c>
+      <c r="I13" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="45">
+        <v>89</v>
+      </c>
+      <c r="K13" s="45">
+        <v>10</v>
+      </c>
+      <c r="L13" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="O13" s="44"/>
+    </row>
+    <row r="14" spans="2:15" ht="72.599999999999994" x14ac:dyDescent="0.3">
+      <c r="B14" s="11">
+        <v>2023</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="L2" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="O2" s="25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="12">
-        <v>2010</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="G3" s="45" t="s">
+      <c r="E14" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="H14" s="44"/>
+      <c r="I14" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="K14" s="45">
+        <v>5</v>
+      </c>
+      <c r="L14" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="45">
-        <v>1445</v>
-      </c>
-      <c r="I3" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="14"/>
-      <c r="O3" s="45"/>
-    </row>
-    <row r="4" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="12">
-        <v>2011</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="G4" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="H4" s="45">
-        <v>253</v>
-      </c>
-      <c r="I4" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="46">
-        <v>2</v>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="14"/>
-      <c r="O4" s="45"/>
-    </row>
-    <row r="5" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="12">
-        <v>2012</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="G5" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="H5" s="45">
-        <v>263</v>
-      </c>
-      <c r="I5" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="46">
-        <v>1</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="14"/>
-      <c r="O5" s="45"/>
-    </row>
-    <row r="6" spans="2:15" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="12">
-        <v>2013</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="45" t="s">
+      <c r="O14" s="44"/>
+    </row>
+    <row r="15" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="11">
+        <v>2024</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="44">
+        <v>2404</v>
+      </c>
+      <c r="E15" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="G6" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="H6" s="45">
-        <v>293</v>
-      </c>
-      <c r="I6" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="46">
-        <v>2</v>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="14"/>
-      <c r="O6" s="45"/>
-    </row>
-    <row r="7" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="12">
-        <v>2015</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="H7" s="45">
-        <v>306</v>
-      </c>
-      <c r="I7" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="46">
-        <v>2</v>
-      </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="14"/>
-      <c r="O7" s="45"/>
-    </row>
-    <row r="8" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="12">
-        <v>2016</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="F15" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="H15" s="44"/>
+      <c r="I15" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="K15" s="45">
         <v>5</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="G8" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="H8" s="45">
-        <v>350</v>
-      </c>
-      <c r="I8" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="46">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="14"/>
-      <c r="O8" s="45"/>
-    </row>
-    <row r="9" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="12">
-        <v>2017</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="G9" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="H9" s="45">
-        <v>1743</v>
-      </c>
-      <c r="I9" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="46" t="s">
+      <c r="L15" s="13"/>
+      <c r="O15" s="44"/>
+    </row>
+    <row r="18" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J18" t="s">
         <v>118</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="14"/>
-      <c r="O9" s="45"/>
-    </row>
-    <row r="10" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="12">
-        <v>2018</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="G10" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="H10" s="45">
-        <v>339</v>
-      </c>
-      <c r="I10" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="46">
-        <v>0</v>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="14"/>
-      <c r="O10" s="45"/>
-    </row>
-    <row r="11" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="12">
-        <v>2019</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="G11" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="H11" s="45">
-        <v>109</v>
-      </c>
-      <c r="I11" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="46">
-        <v>2</v>
-      </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="14"/>
-      <c r="O11" s="45"/>
-    </row>
-    <row r="12" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="12">
-        <v>2020</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="G12" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="H12" s="45"/>
-      <c r="I12" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" s="46">
-        <v>4</v>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="14"/>
-      <c r="O12" s="45"/>
-    </row>
-    <row r="13" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="12">
-        <v>2021</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="G13" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="H13" s="45"/>
-      <c r="I13" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="46">
-        <v>11</v>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="14"/>
-      <c r="O13" s="45"/>
-    </row>
-    <row r="14" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="12">
-        <v>2023</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="G14" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="H14" s="45"/>
-      <c r="I14" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="46">
-        <v>5</v>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="14"/>
-      <c r="O14" s="45"/>
-    </row>
-    <row r="15" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="12">
-        <v>2024</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="G15" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="H15" s="45"/>
-      <c r="I15" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" s="46">
-        <v>4</v>
-      </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="14"/>
-      <c r="O15" s="45"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -2124,55 +2233,55 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:12" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="E3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="14"/>
     </row>
     <row r="4" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17">
+      <c r="B4" s="16">
         <v>2017</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="16">
         <v>555</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <v>448</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="16">
         <f t="shared" ref="E4:E9" si="0">ROUND((C4-D4)/C4, 2)</f>
         <v>0.19</v>
       </c>
-      <c r="F4" s="17">
+      <c r="F4" s="16">
         <v>110</v>
       </c>
-      <c r="G4" s="17">
+      <c r="G4" s="16">
         <f>ROUND((D4-F4)/D4, 2)</f>
         <v>0.75</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="16">
         <v>11</v>
       </c>
       <c r="J4">
@@ -2185,27 +2294,27 @@
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="17">
+      <c r="B5" s="16">
         <v>2023</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="16">
         <v>388</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <v>321</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="16">
         <f t="shared" si="0"/>
         <v>0.17</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="16">
         <v>67</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="16">
         <f t="shared" ref="G5:G9" si="1">ROUND((D5-F5)/D5, 2)</f>
         <v>0.79</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="16">
         <v>9</v>
       </c>
       <c r="J5">
@@ -2218,27 +2327,27 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <v>2024</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="18">
         <v>122</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>87</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <f t="shared" si="0"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="18">
         <v>35</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <v>0</v>
       </c>
       <c r="J6">
@@ -2253,7 +2362,7 @@
     <row r="7" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <f>SUM(C4:C6)</f>
@@ -2278,7 +2387,7 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <f>C9-D9</f>
@@ -2287,26 +2396,26 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
-        <v>55</v>
+      <c r="A17" s="20" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -2319,7 +2428,7 @@
       <c r="D19">
         <v>33</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="19">
         <f>(B19-C19)/B19</f>
         <v>0.80180180180180183</v>
       </c>
@@ -2334,7 +2443,7 @@
       <c r="D20">
         <v>14</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="19">
         <f t="shared" ref="E20:E21" si="2">(B20-C20)/B20</f>
         <v>0.82731958762886593</v>
       </c>
@@ -2349,32 +2458,32 @@
       <c r="D21">
         <v>10</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="19">
         <f t="shared" si="2"/>
         <v>0.71311475409836067</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="21">
+      <c r="A22" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="20">
         <f>SUM(B19:B21)</f>
         <v>1065</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="20">
         <f>SUM(C19:C21)</f>
         <v>212</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="20">
         <f>SUM(D19:D21)</f>
         <v>57</v>
       </c>
-      <c r="E22" s="21"/>
+      <c r="E22" s="20"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B24">
         <f>1068-755</f>
@@ -2383,7 +2492,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B25">
         <f>755-212</f>
@@ -2391,37 +2500,37 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="21">
+      <c r="A26" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="20">
         <f>B24+B25</f>
         <v>856</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="22">
+      <c r="A28" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="21">
         <f>B26/B22</f>
         <v>0.8037558685446009</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" s="20">
+      <c r="A30" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="19">
         <f>AVERAGE(E19:E21)</f>
         <v>0.78074538117634285</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" s="20">
+        <v>41</v>
+      </c>
+      <c r="B31" s="19">
         <f>MEDIAN(E19:E21)</f>
         <v>0.80180180180180183</v>
       </c>
@@ -2445,33 +2554,33 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
     </row>
     <row r="4" spans="2:7" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="4"/>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="5" spans="2:7" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <v>2017</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>522</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>12</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>21</v>
       </c>
       <c r="F5">
@@ -2484,16 +2593,16 @@
       </c>
     </row>
     <row r="6" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>2023</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <v>374</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>9</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="9">
         <v>5</v>
       </c>
       <c r="F6">
@@ -2506,16 +2615,16 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>2024</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <v>122</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>5</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <v>5</v>
       </c>
       <c r="F7">
@@ -2528,40 +2637,40 @@
       </c>
     </row>
     <row r="8" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
     </row>
     <row r="13" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
+++ b/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvonne.barkley\Github\BANTER_Pseudorca\manuscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422453C3-F1C3-4191-A16E-F118B3234197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F106ECE8-F7DF-46D5-A0CC-77E0A6645308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44220" yWindow="5820" windowWidth="17280" windowHeight="10695" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39885" yWindow="6105" windowWidth="20475" windowHeight="13395" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Threshold_Table" sheetId="4" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="176">
   <si>
     <t>Survey Year</t>
   </si>
@@ -205,24 +205,15 @@
     <t>Jen Math :)</t>
   </si>
   <si>
-    <t>Suvery Year</t>
-  </si>
-  <si>
     <t>Banter Threshold</t>
   </si>
   <si>
-    <t>Raw</t>
-  </si>
-  <si>
     <t xml:space="preserve">SA </t>
   </si>
   <si>
     <t xml:space="preserve">SSC </t>
   </si>
   <si>
-    <t xml:space="preserve">Raw </t>
-  </si>
-  <si>
     <t>69 (36)</t>
   </si>
   <si>
@@ -386,9 +377,6 @@
   </si>
   <si>
     <t>10; 11</t>
-  </si>
-  <si>
-    <t>(false positives)</t>
   </si>
   <si>
     <t>SA &amp; SSC</t>
@@ -493,6 +481,168 @@
   <si>
     <t>Yano, K. M., Oleson, E. M., Keating, J. L., Ballance, L. T., Hill, M. C., Bradford, A. L., Allen, A. N., Joyce, T. W., Moore, J. E., &amp; Henry, A. E. (2018). Cetacean and Seabird Data Collected during the Hawaiian Islands Cetacean and Ecosystem Assessment Survey (HICEAS), July—December 2017. NOAA Technical Memorandum NMFS-PIFSC-72</t>
   </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>69 (52%)</t>
+  </si>
+  <si>
+    <t>55 (40%)</t>
+  </si>
+  <si>
+    <t>40 (28%)</t>
+  </si>
+  <si>
+    <t>27 (7%)</t>
+  </si>
+  <si>
+    <t>44 (25%)</t>
+  </si>
+  <si>
+    <t>41 (20%)</t>
+  </si>
+  <si>
+    <t>33 (12%)</t>
+  </si>
+  <si>
+    <t>55 (45%)</t>
+  </si>
+  <si>
+    <t>44 (32%)</t>
+  </si>
+  <si>
+    <t>36 (19%)</t>
+  </si>
+  <si>
+    <t>6 (0%)</t>
+  </si>
+  <si>
+    <t>25 (0%)</t>
+  </si>
+  <si>
+    <t>33 (0%)</t>
+  </si>
+  <si>
+    <t>29 (0%)</t>
+  </si>
+  <si>
+    <t>3 (0%)</t>
+  </si>
+  <si>
+    <t>4 (0%)</t>
+  </si>
+  <si>
+    <t>8 (0%)</t>
+  </si>
+  <si>
+    <t>10 (0%)</t>
+  </si>
+  <si>
+    <t>14 (0%)</t>
+  </si>
+  <si>
+    <t>9 (0%)</t>
+  </si>
+  <si>
+    <t>12 (0%)</t>
+  </si>
+  <si>
+    <t>57 (0%)</t>
+  </si>
+  <si>
+    <t>52 (0%)</t>
+  </si>
+  <si>
+    <t>45 (0%)</t>
+  </si>
+  <si>
+    <t>35 (0%)</t>
+  </si>
+  <si>
+    <t>51 (73%)</t>
+  </si>
+  <si>
+    <t>31 (68%)</t>
+  </si>
+  <si>
+    <t>21 (62%)</t>
+  </si>
+  <si>
+    <t>6 (33%)</t>
+  </si>
+  <si>
+    <t>33 (58%)</t>
+  </si>
+  <si>
+    <t>17 (41%)</t>
+  </si>
+  <si>
+    <t>12 (33%)</t>
+  </si>
+  <si>
+    <t>5 (20%)</t>
+  </si>
+  <si>
+    <t>30 (60%)</t>
+  </si>
+  <si>
+    <t>24 (58%)</t>
+  </si>
+  <si>
+    <t>17 (53%)</t>
+  </si>
+  <si>
+    <t>14 (29%)</t>
+  </si>
+  <si>
+    <t>10 (10%)</t>
+  </si>
+  <si>
+    <t>9 (11%)</t>
+  </si>
+  <si>
+    <t>13 (23%)</t>
+  </si>
+  <si>
+    <t>11 (9%)</t>
+  </si>
+  <si>
+    <t>134 (57%)</t>
+  </si>
+  <si>
+    <t>96 (46%)</t>
+  </si>
+  <si>
+    <t>70 (36%)</t>
+  </si>
+  <si>
+    <t>39 (10%)</t>
+  </si>
+  <si>
+    <t>90 (37%)</t>
+  </si>
+  <si>
+    <t>67 (22%)</t>
+  </si>
+  <si>
+    <t>53 (15%)</t>
+  </si>
+  <si>
+    <t>36 (3%)</t>
+  </si>
+  <si>
+    <t>78 (37%)</t>
+  </si>
+  <si>
+    <t>62 (27%)</t>
+  </si>
+  <si>
+    <t>38 (8%)</t>
+  </si>
+  <si>
+    <t>Classification Threshold</t>
+  </si>
 </sst>
 </file>
 
@@ -501,7 +651,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -598,6 +748,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -619,7 +784,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -905,11 +1070,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1034,8 +1225,101 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1317,20 +1601,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16B82A36-BAB4-4DA2-945D-9C525C938092}">
-  <dimension ref="B1:R14"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:R28"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="23"/>
-    <col min="2" max="2" width="15.33203125" style="22" customWidth="1"/>
-    <col min="3" max="18" width="12.44140625" style="23" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="23"/>
+    <col min="1" max="1" width="9.140625" style="23"/>
+    <col min="2" max="2" width="16.7109375" style="22" customWidth="1"/>
+    <col min="3" max="18" width="12.42578125" style="23" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:18" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="25"/>
       <c r="C2" s="26" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="D2" s="27"/>
       <c r="E2" s="27"/>
@@ -1348,9 +1632,9 @@
       <c r="Q2" s="29"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="2:18" ht="42" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:18" ht="42" x14ac:dyDescent="0.35">
       <c r="B3" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" s="32">
         <v>2017</v>
@@ -1377,328 +1661,1025 @@
       <c r="Q3" s="29"/>
       <c r="R3" s="31"/>
     </row>
-    <row r="4" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:18" ht="21" x14ac:dyDescent="0.35">
       <c r="B4" s="34"/>
       <c r="C4" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>47</v>
-      </c>
       <c r="F4" s="37" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="K4" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="L4" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="M4" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="N4" s="37" t="s">
-        <v>105</v>
+        <v>101</v>
+      </c>
+      <c r="K4" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="L4" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="56" t="s">
+        <v>101</v>
       </c>
       <c r="O4" s="35" t="s">
-        <v>48</v>
+        <v>122</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R4" s="37" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" ht="21" x14ac:dyDescent="0.35">
       <c r="B5" s="38">
         <v>0.5</v>
       </c>
       <c r="C5" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="G5" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="H5" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="I5" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="J5" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="K5" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="36" t="s">
+      <c r="L5" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="M5" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="K5" s="35" t="s">
+      <c r="N5" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="L5" s="36" t="s">
+      <c r="O5" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="M5" s="36" t="s">
+      <c r="P5" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="N5" s="37" t="s">
+      <c r="Q5" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="O5" s="35" t="s">
+      <c r="R5" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="P5" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q5" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="R5" s="37" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="2:18" ht="21" x14ac:dyDescent="0.35">
       <c r="B6" s="38">
         <v>0.6</v>
       </c>
       <c r="C6" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="H6" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="I6" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="35" t="s">
+      <c r="J6" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="H6" s="36" t="s">
+      <c r="L6" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="I6" s="36" t="s">
+      <c r="M6" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="O6" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="P6" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="J6" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" s="35" t="s">
+      <c r="Q6" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="L6" s="36" t="s">
+      <c r="R6" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="M6" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="N6" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="O6" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="P6" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q6" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="R6" s="37" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="2:18" ht="21" x14ac:dyDescent="0.35">
       <c r="B7" s="38">
         <v>0.7</v>
       </c>
       <c r="C7" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="G7" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="H7" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="I7" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="35" t="s">
+      <c r="J7" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="36" t="s">
+      <c r="K7" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="I7" s="36" t="s">
+      <c r="L7" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="M7" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="N7" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="O7" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="P7" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="35" t="s">
+      <c r="Q7" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="L7" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="M7" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="N7" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="O7" s="35" t="s">
+      <c r="R7" s="37" t="s">
         <v>85</v>
       </c>
-      <c r="P7" s="36" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q7" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="R7" s="37" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="2:18" ht="21" x14ac:dyDescent="0.35">
       <c r="B8" s="38">
         <v>0.8</v>
       </c>
       <c r="C8" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="F8" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="I8" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="J8" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="F8" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="35" t="s">
+      <c r="K8" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="36" t="s">
+      <c r="L8" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="M8" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="N8" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="O8" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="I8" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="J8" s="37" t="s">
+      <c r="P8" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="K8" s="35" t="s">
+      <c r="Q8" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="L8" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="M8" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="N8" s="37" t="s">
-        <v>94</v>
-      </c>
-      <c r="O8" s="35" t="s">
+      <c r="R8" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="P8" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q8" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="R8" s="37" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="2:18" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="39">
         <v>0.9</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E9" s="41" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G9" s="40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H9" s="41" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I9" s="41" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J9" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="K9" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="L9" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="M9" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="N9" s="42" t="s">
-        <v>99</v>
+        <v>96</v>
+      </c>
+      <c r="K9" s="57" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="M9" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="N9" s="59" t="s">
+        <v>96</v>
       </c>
       <c r="O9" s="40" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P9" s="41" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q9" s="41" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="R9" s="42" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="C14" s="23" t="s">
-        <v>104</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="B10" s="52"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="53"/>
+    </row>
+    <row r="11" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="C11" s="48"/>
+    </row>
+    <row r="12" spans="2:18" s="49" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="C12" s="50">
+        <f>36/VALUE(TRIM(LEFT(C5, FIND("(", C5) - 1)))</f>
+        <v>0.52173913043478259</v>
+      </c>
+      <c r="D12" s="50">
+        <f>11/VALUE(TRIM(LEFT(D5, FIND("(", D5) - 1)))</f>
+        <v>0.25</v>
+      </c>
+      <c r="E12" s="50">
+        <f>25/VALUE(TRIM(LEFT(E5, FIND("(", E5) - 1)))</f>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="F12" s="50">
+        <v>0</v>
+      </c>
+      <c r="G12" s="50">
+        <f>37/VALUE(TRIM(LEFT(G5, FIND("(", G5) - 1)))</f>
+        <v>0.72549019607843135</v>
+      </c>
+      <c r="H12" s="50">
+        <f>19/VALUE(TRIM(LEFT(H5, FIND("(", H5) - 1)))</f>
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="I12" s="50">
+        <f>18/VALUE(TRIM(LEFT(I5, FIND("(", I5) - 1)))</f>
+        <v>0.6</v>
+      </c>
+      <c r="J12" s="50">
+        <v>0</v>
+      </c>
+      <c r="K12" s="50">
+        <f>4/VALUE(TRIM(LEFT(K5, FIND("(", K5) - 1)))</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="L12" s="50">
+        <f>3/VALUE(TRIM(LEFT(L5, FIND("(", L5) - 1)))</f>
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="M12" s="50">
+        <f>1/VALUE(TRIM(LEFT(M5, FIND("(", M5) - 1)))</f>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="N12" s="50">
+        <v>0</v>
+      </c>
+      <c r="O12" s="50">
+        <f>77/VALUE(TRIM(LEFT(O5, FIND("(", O5) - 1)))</f>
+        <v>0.57462686567164178</v>
+      </c>
+      <c r="P12" s="50">
+        <f>33/VALUE(TRIM(LEFT(P5, FIND("(", P5) - 1)))</f>
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="Q12" s="50">
+        <f>44/VALUE(TRIM(LEFT(Q5, FIND("(", Q5) - 1)))</f>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="R12" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" s="49" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B13" s="51"/>
+      <c r="C13" s="50">
+        <f>22/VALUE(TRIM(LEFT(C6, FIND("(", C6) - 1)))</f>
+        <v>0.4</v>
+      </c>
+      <c r="D13" s="50">
+        <f>8/VALUE(TRIM(LEFT(D6, FIND("(", D6) - 1)))</f>
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="E13" s="50">
+        <f>14/VALUE(TRIM(LEFT(E6, FIND("(", E6) - 1)))</f>
+        <v>0.31818181818181818</v>
+      </c>
+      <c r="F13" s="50">
+        <v>0</v>
+      </c>
+      <c r="G13" s="50">
+        <f>21/VALUE(TRIM(LEFT(G6, FIND("(", G6) - 1)))</f>
+        <v>0.67741935483870963</v>
+      </c>
+      <c r="H13" s="50">
+        <f>7/VALUE(TRIM(LEFT(H6, FIND("(", H6) - 1)))</f>
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="I13" s="50">
+        <f>14/VALUE(TRIM(LEFT(I6, FIND("(", I6) - 1)))</f>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="J13" s="50">
+        <v>0</v>
+      </c>
+      <c r="K13" s="50">
+        <f>1/VALUE(TRIM(LEFT(K6, FIND("(", K6) - 1)))</f>
+        <v>0.1</v>
+      </c>
+      <c r="L13" s="50">
+        <v>0</v>
+      </c>
+      <c r="M13" s="50">
+        <f>1/VALUE(TRIM(LEFT(M6, FIND("(", M6) - 1)))</f>
+        <v>0.1</v>
+      </c>
+      <c r="N13" s="50">
+        <v>0</v>
+      </c>
+      <c r="O13" s="50">
+        <f>44/VALUE(TRIM(LEFT(O6, FIND("(", O6) - 1)))</f>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="P13" s="50">
+        <f>15/VALUE(TRIM(LEFT(P6, FIND("(", P6) - 1)))</f>
+        <v>0.22388059701492538</v>
+      </c>
+      <c r="Q13" s="50">
+        <f>29/VALUE(TRIM(LEFT(Q6, FIND("(", Q6) - 1)))</f>
+        <v>0.37179487179487181</v>
+      </c>
+      <c r="R13" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" s="49" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B14" s="51"/>
+      <c r="C14" s="50">
+        <f>11/VALUE(TRIM(LEFT(C7, FIND("(", C7) - 1)))</f>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="D14" s="50">
+        <f>4/VALUE(TRIM(LEFT(D7, FIND("(", D7) - 1)))</f>
+        <v>0.12121212121212122</v>
+      </c>
+      <c r="E14" s="50">
+        <f>7/VALUE(TRIM(LEFT(E7, FIND("(", E7) - 1)))</f>
+        <v>0.19444444444444445</v>
+      </c>
+      <c r="F14" s="50">
+        <v>0</v>
+      </c>
+      <c r="G14" s="50">
+        <f>13/VALUE(TRIM(LEFT(G7, FIND("(", G7) - 1)))</f>
+        <v>0.61904761904761907</v>
+      </c>
+      <c r="H14" s="50">
+        <f>4/VALUE(TRIM(LEFT(H7, FIND("(", H7) - 1)))</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I14" s="50">
+        <f>9/VALUE(TRIM(LEFT(I7, FIND("(", I7) - 1)))</f>
+        <v>0.52941176470588236</v>
+      </c>
+      <c r="J14" s="50">
+        <v>0</v>
+      </c>
+      <c r="K14" s="50">
+        <f>1/VALUE(TRIM(LEFT(K7, FIND("(", K7) - 1)))</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="L14" s="50">
+        <v>0</v>
+      </c>
+      <c r="M14" s="50">
+        <f>1/VALUE(TRIM(LEFT(M7, FIND("(", M7) - 1)))</f>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="N14" s="50">
+        <v>0</v>
+      </c>
+      <c r="O14" s="50">
+        <f>25/VALUE(TRIM(LEFT(O7, FIND("(", O7) - 1)))</f>
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="P14" s="50">
+        <f>8/VALUE(TRIM(LEFT(P7, FIND("(", P7) - 1)))</f>
+        <v>0.15094339622641509</v>
+      </c>
+      <c r="Q14" s="50">
+        <f>17/VALUE(TRIM(LEFT(Q7, FIND("(", Q7) - 1)))</f>
+        <v>0.27419354838709675</v>
+      </c>
+      <c r="R14" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" s="49" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B15" s="51"/>
+      <c r="C15" s="50">
+        <f>2/VALUE(TRIM(LEFT(C8, FIND("(", C8) - 1)))</f>
+        <v>7.407407407407407E-2</v>
+      </c>
+      <c r="D15" s="50">
+        <f>0/VALUE(TRIM(LEFT(D8, FIND("(", D8) - 1)))</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="50">
+        <f>2/VALUE(TRIM(LEFT(E8, FIND("(", E8) - 1)))</f>
+        <v>7.407407407407407E-2</v>
+      </c>
+      <c r="F15" s="50">
+        <v>0</v>
+      </c>
+      <c r="G15" s="50">
+        <f>2/VALUE(TRIM(LEFT(G8, FIND("(", G8) - 1)))</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="H15" s="50">
+        <f>1/VALUE(TRIM(LEFT(H8, FIND("(", H8) - 1)))</f>
+        <v>0.2</v>
+      </c>
+      <c r="I15" s="50">
+        <f>1/VALUE(TRIM(LEFT(I8, FIND("(", I8) - 1)))</f>
+        <v>0.2</v>
+      </c>
+      <c r="J15" s="50">
+        <v>0</v>
+      </c>
+      <c r="K15" s="50">
+        <v>0</v>
+      </c>
+      <c r="L15" s="50">
+        <v>0</v>
+      </c>
+      <c r="M15" s="50">
+        <v>0</v>
+      </c>
+      <c r="N15" s="50">
+        <v>0</v>
+      </c>
+      <c r="O15" s="50">
+        <f>4/VALUE(TRIM(LEFT(O8, FIND("(", O8) - 1)))</f>
+        <v>0.10256410256410256</v>
+      </c>
+      <c r="P15" s="50">
+        <f>1/VALUE(TRIM(LEFT(P8, FIND("(", P8) - 1)))</f>
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="Q15" s="50">
+        <f>3/VALUE(TRIM(LEFT(Q8, FIND("(", Q8) - 1)))</f>
+        <v>7.8947368421052627E-2</v>
+      </c>
+      <c r="R15" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" s="49" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B16" s="51"/>
+      <c r="C16" s="50">
+        <f>0/VALUE(TRIM(LEFT(C9, FIND("(", C9) - 1)))</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="50">
+        <f>0/VALUE(TRIM(LEFT(D9, FIND("(", D9) - 1)))</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="50">
+        <f>0/VALUE(TRIM(LEFT(E9, FIND("(", E9) - 1)))</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="50">
+        <v>0</v>
+      </c>
+      <c r="G16" s="50">
+        <f>0/VALUE(TRIM(LEFT(G9, FIND("(", G9) - 1)))</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="50">
+        <f>0/VALUE(TRIM(LEFT(H9, FIND("(", H9) - 1)))</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="50">
+        <f>0/VALUE(TRIM(LEFT(I9, FIND("(", I9) - 1)))</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="50">
+        <v>0</v>
+      </c>
+      <c r="K16" s="50">
+        <v>0</v>
+      </c>
+      <c r="L16" s="50">
+        <v>0</v>
+      </c>
+      <c r="M16" s="50">
+        <v>0</v>
+      </c>
+      <c r="N16" s="50">
+        <v>0</v>
+      </c>
+      <c r="O16" s="50">
+        <v>0</v>
+      </c>
+      <c r="P16" s="50">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="50">
+        <v>0</v>
+      </c>
+      <c r="R16" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" s="49" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="K17" s="51"/>
+      <c r="O17" s="51"/>
+    </row>
+    <row r="20" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:18" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="25"/>
+      <c r="C21" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="76"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="76"/>
+      <c r="J21" s="76"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="76"/>
+      <c r="M21" s="76"/>
+      <c r="N21" s="76"/>
+      <c r="O21" s="76"/>
+      <c r="P21" s="76"/>
+      <c r="Q21" s="76"/>
+      <c r="R21" s="77"/>
+    </row>
+    <row r="22" spans="2:18" ht="42" x14ac:dyDescent="0.35">
+      <c r="B22" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="C22" s="61">
+        <v>2017</v>
+      </c>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="61">
+        <v>2023</v>
+      </c>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="63"/>
+      <c r="K22" s="61">
+        <v>2024</v>
+      </c>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="64"/>
+      <c r="R22" s="65"/>
+    </row>
+    <row r="23" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="B23" s="66"/>
+      <c r="C23" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="H23" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="K23" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="L23" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="M23" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="N23" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="O23" s="67" t="s">
+        <v>122</v>
+      </c>
+      <c r="P23" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q23" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="R23" s="69" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="B24" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="C24" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="68" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" s="69" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="67" t="s">
+        <v>148</v>
+      </c>
+      <c r="H24" s="68" t="s">
+        <v>152</v>
+      </c>
+      <c r="I24" s="68" t="s">
+        <v>156</v>
+      </c>
+      <c r="J24" s="69" t="s">
+        <v>141</v>
+      </c>
+      <c r="K24" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="L24" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="M24" s="68" t="s">
+        <v>163</v>
+      </c>
+      <c r="N24" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="O24" s="67" t="s">
+        <v>164</v>
+      </c>
+      <c r="P24" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q24" s="68" t="s">
+        <v>165</v>
+      </c>
+      <c r="R24" s="69" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="B25" s="70">
+        <v>0.6</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="68" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" s="69" t="s">
+        <v>135</v>
+      </c>
+      <c r="G25" s="67" t="s">
+        <v>149</v>
+      </c>
+      <c r="H25" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="I25" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="J25" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="K25" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="L25" s="68" t="s">
+        <v>142</v>
+      </c>
+      <c r="M25" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="N25" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="O25" s="67" t="s">
+        <v>165</v>
+      </c>
+      <c r="P25" s="68" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q25" s="68" t="s">
+        <v>172</v>
+      </c>
+      <c r="R25" s="69" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="B26" s="70">
+        <v>0.7</v>
+      </c>
+      <c r="C26" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="68" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="69" t="s">
+        <v>136</v>
+      </c>
+      <c r="G26" s="67" t="s">
+        <v>150</v>
+      </c>
+      <c r="H26" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="I26" s="68" t="s">
+        <v>158</v>
+      </c>
+      <c r="J26" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="K26" s="67" t="s">
+        <v>161</v>
+      </c>
+      <c r="L26" s="68" t="s">
+        <v>139</v>
+      </c>
+      <c r="M26" s="68" t="s">
+        <v>161</v>
+      </c>
+      <c r="N26" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="O26" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="P26" s="68" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q26" s="68" t="s">
+        <v>173</v>
+      </c>
+      <c r="R26" s="69" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+      <c r="B27" s="70">
+        <v>0.8</v>
+      </c>
+      <c r="C27" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="F27" s="69" t="s">
+        <v>134</v>
+      </c>
+      <c r="G27" s="67" t="s">
+        <v>151</v>
+      </c>
+      <c r="H27" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="I27" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="J27" s="69" t="s">
+        <v>138</v>
+      </c>
+      <c r="K27" s="67" t="s">
+        <v>133</v>
+      </c>
+      <c r="L27" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="M27" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="N27" s="69" t="s">
+        <v>133</v>
+      </c>
+      <c r="O27" s="67" t="s">
+        <v>167</v>
+      </c>
+      <c r="P27" s="68" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q27" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="R27" s="69" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="71">
+        <v>0.9</v>
+      </c>
+      <c r="C28" s="72" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="F28" s="74" t="s">
+        <v>133</v>
+      </c>
+      <c r="G28" s="72" t="s">
+        <v>137</v>
+      </c>
+      <c r="H28" s="73" t="s">
+        <v>137</v>
+      </c>
+      <c r="I28" s="73" t="s">
+        <v>137</v>
+      </c>
+      <c r="J28" s="74" t="s">
+        <v>137</v>
+      </c>
+      <c r="K28" s="72" t="s">
+        <v>137</v>
+      </c>
+      <c r="L28" s="73" t="s">
+        <v>137</v>
+      </c>
+      <c r="M28" s="73" t="s">
+        <v>137</v>
+      </c>
+      <c r="N28" s="74" t="s">
+        <v>137</v>
+      </c>
+      <c r="O28" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="P28" s="73" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q28" s="73" t="s">
+        <v>143</v>
+      </c>
+      <c r="R28" s="74" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C21:R21"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1707,15 +2688,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:O18"/>
-  <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.21875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="35.109375" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="35.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:15" ht="83.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
@@ -1732,28 +2713,28 @@
         <v>13</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>15</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O2" s="24" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:15" ht="68.25" x14ac:dyDescent="0.25">
       <c r="B3" s="11">
         <v>2010</v>
       </c>
@@ -1761,16 +2742,16 @@
         <v>4</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E3" s="44" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H3" s="44">
         <v>1445</v>
@@ -1779,17 +2760,17 @@
         <v>14</v>
       </c>
       <c r="J3" s="45" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K3" s="45" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L3" s="46" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="O3" s="44"/>
     </row>
-    <row r="4" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11">
         <v>2011</v>
       </c>
@@ -1803,10 +2784,10 @@
         <v>9</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H4" s="44">
         <v>253</v>
@@ -1823,7 +2804,7 @@
       <c r="L4" s="13"/>
       <c r="O4" s="44"/>
     </row>
-    <row r="5" spans="2:15" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:15" ht="57" x14ac:dyDescent="0.25">
       <c r="B5" s="11">
         <v>2012</v>
       </c>
@@ -1837,10 +2818,10 @@
         <v>9</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H5" s="44">
         <v>263</v>
@@ -1855,11 +2836,11 @@
         <v>1</v>
       </c>
       <c r="L5" s="46" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="O5" s="44"/>
     </row>
-    <row r="6" spans="2:15" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:15" ht="57" x14ac:dyDescent="0.25">
       <c r="B6" s="11">
         <v>2013</v>
       </c>
@@ -1873,10 +2854,10 @@
         <v>10</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G6" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H6" s="44">
         <v>293</v>
@@ -1891,11 +2872,11 @@
         <v>2</v>
       </c>
       <c r="L6" s="46" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="O6" s="44"/>
     </row>
-    <row r="7" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="11">
         <v>2015</v>
       </c>
@@ -1909,10 +2890,10 @@
         <v>11</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G7" s="44" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H7" s="44">
         <v>306</v>
@@ -1929,7 +2910,7 @@
       <c r="L7" s="13"/>
       <c r="O7" s="44"/>
     </row>
-    <row r="8" spans="2:15" ht="52.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" ht="57" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
         <v>2016</v>
       </c>
@@ -1943,10 +2924,10 @@
         <v>11</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G8" s="44" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H8" s="44">
         <v>350</v>
@@ -1961,11 +2942,11 @@
         <v>1</v>
       </c>
       <c r="L8" s="46" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="O8" s="44"/>
     </row>
-    <row r="9" spans="2:15" ht="109.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" ht="109.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <v>2017</v>
       </c>
@@ -1973,16 +2954,16 @@
         <v>4</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E9" s="44" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G9" s="44" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H9" s="44">
         <v>1743</v>
@@ -1991,17 +2972,17 @@
         <v>16</v>
       </c>
       <c r="J9" s="45" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K9" s="45" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L9" s="47" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="O9" s="44"/>
     </row>
-    <row r="10" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11">
         <v>2018</v>
       </c>
@@ -2015,10 +2996,10 @@
         <v>11</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H10" s="44">
         <v>339</v>
@@ -2035,7 +3016,7 @@
       <c r="L10" s="13"/>
       <c r="O10" s="44"/>
     </row>
-    <row r="11" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="11">
         <v>2019</v>
       </c>
@@ -2049,10 +3030,10 @@
         <v>11</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G11" s="44" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H11" s="44">
         <v>109</v>
@@ -2069,7 +3050,7 @@
       <c r="L11" s="13"/>
       <c r="O11" s="44"/>
     </row>
-    <row r="12" spans="2:15" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="11">
         <v>2020</v>
       </c>
@@ -2083,10 +3064,10 @@
         <v>11</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H12" s="44">
         <v>475</v>
@@ -2101,11 +3082,11 @@
         <v>4</v>
       </c>
       <c r="L12" s="46" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="O12" s="44"/>
     </row>
-    <row r="13" spans="2:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" ht="68.25" x14ac:dyDescent="0.25">
       <c r="B13" s="11">
         <v>2021</v>
       </c>
@@ -2119,10 +3100,10 @@
         <v>11</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H13" s="44">
         <v>339</v>
@@ -2137,11 +3118,11 @@
         <v>10</v>
       </c>
       <c r="L13" s="46" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="O13" s="44"/>
     </row>
-    <row r="14" spans="2:15" ht="72.599999999999994" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" ht="79.5" x14ac:dyDescent="0.25">
       <c r="B14" s="11">
         <v>2023</v>
       </c>
@@ -2149,38 +3130,41 @@
         <v>4</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E14" s="44" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="H14" s="44"/>
+        <v>104</v>
+      </c>
+      <c r="H14" s="79">
+        <f>733+435</f>
+        <v>1168</v>
+      </c>
       <c r="I14" s="45" t="s">
         <v>18</v>
       </c>
       <c r="J14" s="45" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K14" s="45">
         <v>5</v>
       </c>
       <c r="L14" s="46" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="O14" s="44"/>
     </row>
-    <row r="15" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="11">
         <v>2024</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D15" s="44">
         <v>2404</v>
@@ -2189,17 +3173,19 @@
         <v>11</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="H15" s="44"/>
+        <v>104</v>
+      </c>
+      <c r="H15" s="44">
+        <v>389</v>
+      </c>
       <c r="I15" s="45" t="s">
         <v>18</v>
       </c>
       <c r="J15" s="45" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K15" s="45">
         <v>5</v>
@@ -2207,9 +3193,9 @@
       <c r="L15" s="13"/>
       <c r="O15" s="44"/>
     </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J18" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2223,16 +3209,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C3CA73-E650-4EB7-93C1-D459BAC41A38}">
   <dimension ref="A3:L31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" customWidth="1"/>
-    <col min="6" max="12" width="10.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="12" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:12" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="17" t="s">
         <v>0</v>
       </c>
@@ -2260,7 +3246,7 @@
       </c>
       <c r="L3" s="14"/>
     </row>
-    <row r="4" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B4" s="16">
         <v>2017</v>
       </c>
@@ -2271,7 +3257,7 @@
         <v>448</v>
       </c>
       <c r="E4" s="16">
-        <f t="shared" ref="E4:E9" si="0">ROUND((C4-D4)/C4, 2)</f>
+        <f>ROUND((C4-D4)/C4, 2)</f>
         <v>0.19</v>
       </c>
       <c r="F4" s="16">
@@ -2293,7 +3279,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="16">
         <v>2023</v>
       </c>
@@ -2304,7 +3290,7 @@
         <v>321</v>
       </c>
       <c r="E5" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E5:E9" si="0">ROUND((C5-D5)/C5, 2)</f>
         <v>0.17</v>
       </c>
       <c r="F5" s="16">
@@ -2326,7 +3312,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="18">
         <v>2024</v>
       </c>
@@ -2359,8 +3345,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>29</v>
       </c>
@@ -2385,7 +3371,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>28</v>
       </c>
@@ -2394,17 +3380,17 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>32</v>
       </c>
@@ -2418,7 +3404,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>555</v>
       </c>
@@ -2433,7 +3419,7 @@
         <v>0.80180180180180183</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>388</v>
       </c>
@@ -2448,7 +3434,7 @@
         <v>0.82731958762886593</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>122</v>
       </c>
@@ -2463,7 +3449,7 @@
         <v>0.71311475409836067</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>32</v>
       </c>
@@ -2481,7 +3467,7 @@
       </c>
       <c r="E22" s="20"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -2490,7 +3476,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -2499,7 +3485,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>38</v>
       </c>
@@ -2508,7 +3494,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
         <v>39</v>
       </c>
@@ -2517,7 +3503,7 @@
         <v>0.8037558685446009</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
         <v>40</v>
       </c>
@@ -2526,7 +3512,7 @@
         <v>0.78074538117634285</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>41</v>
       </c>
@@ -2544,21 +3530,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC43C8DF-330E-4085-938E-0299F38AFB9F}">
   <dimension ref="B3:G13"/>
-  <sheetFormatPr defaultColWidth="21.5546875" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="21.5703125" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-    </row>
-    <row r="4" spans="2:7" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+    </row>
+    <row r="4" spans="2:7" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3"/>
       <c r="C4" s="6" t="s">
         <v>19</v>
@@ -2570,7 +3556,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10">
         <v>2017</v>
       </c>
@@ -2592,7 +3578,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <v>2023</v>
       </c>
@@ -2614,7 +3600,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5">
         <v>2024</v>
       </c>
@@ -2636,37 +3622,37 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>

--- a/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
+++ b/manuscript/BANTER_Pseudorca-AllTablesxlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvonne.barkley\Github\BANTER_Pseudorca\manuscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F106ECE8-F7DF-46D5-A0CC-77E0A6645308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31A87765-4EB8-4DC5-9A57-8D478B68876A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39885" yWindow="6105" windowWidth="20475" windowHeight="13395" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47010" yWindow="4890" windowWidth="17985" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Threshold_Table" sheetId="4" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="VVAO" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -764,7 +765,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -783,6 +784,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="25">
     <border>
@@ -1100,7 +1113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1243,24 +1256,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1306,20 +1301,59 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1602,16 +1636,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16B82A36-BAB4-4DA2-945D-9C525C938092}">
   <dimension ref="B1:R28"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="23"/>
-    <col min="2" max="2" width="16.7109375" style="22" customWidth="1"/>
-    <col min="3" max="18" width="12.42578125" style="23" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="23"/>
+    <col min="1" max="1" width="9.109375" style="23"/>
+    <col min="2" max="2" width="16.6640625" style="22" customWidth="1"/>
+    <col min="3" max="18" width="12.44140625" style="23" customWidth="1"/>
+    <col min="19" max="16384" width="9.109375" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:18" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="25"/>
       <c r="C2" s="26" t="s">
         <v>0</v>
@@ -1632,7 +1666,7 @@
       <c r="Q2" s="29"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="2:18" ht="42" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:18" ht="42" x14ac:dyDescent="0.4">
       <c r="B3" s="43" t="s">
         <v>43</v>
       </c>
@@ -1661,7 +1695,7 @@
       <c r="Q3" s="29"/>
       <c r="R3" s="31"/>
     </row>
-    <row r="4" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:18" ht="21" x14ac:dyDescent="0.4">
       <c r="B4" s="34"/>
       <c r="C4" s="35" t="s">
         <v>122</v>
@@ -1687,32 +1721,32 @@
       <c r="J4" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="54" t="s">
+      <c r="K4" s="70" t="s">
         <v>122</v>
       </c>
-      <c r="L4" s="55" t="s">
+      <c r="L4" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="M4" s="55" t="s">
+      <c r="M4" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="56" t="s">
+      <c r="N4" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="O4" s="35" t="s">
+      <c r="O4" s="76" t="s">
         <v>122</v>
       </c>
-      <c r="P4" s="36" t="s">
+      <c r="P4" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="Q4" s="36" t="s">
+      <c r="Q4" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="R4" s="37" t="s">
+      <c r="R4" s="78" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:18" ht="21" x14ac:dyDescent="0.4">
       <c r="B5" s="38">
         <v>0.5</v>
       </c>
@@ -1725,7 +1759,7 @@
       <c r="E5" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="86" t="s">
         <v>49</v>
       </c>
       <c r="G5" s="35" t="s">
@@ -1737,35 +1771,35 @@
       <c r="I5" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J5" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="54" t="s">
+      <c r="K5" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="L5" s="55" t="s">
+      <c r="L5" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="55" t="s">
+      <c r="M5" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="N5" s="56" t="s">
+      <c r="N5" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="O5" s="35" t="s">
+      <c r="O5" s="76" t="s">
         <v>58</v>
       </c>
-      <c r="P5" s="36" t="s">
+      <c r="P5" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="Q5" s="36" t="s">
+      <c r="Q5" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="R5" s="37" t="s">
+      <c r="R5" s="78" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:18" ht="21" x14ac:dyDescent="0.4">
       <c r="B6" s="38">
         <v>0.6</v>
       </c>
@@ -1793,32 +1827,32 @@
       <c r="J6" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="54" t="s">
+      <c r="K6" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="L6" s="55" t="s">
+      <c r="L6" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="M6" s="55" t="s">
+      <c r="M6" s="71" t="s">
         <v>68</v>
       </c>
-      <c r="N6" s="56" t="s">
+      <c r="N6" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="O6" s="35" t="s">
+      <c r="O6" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="P6" s="36" t="s">
+      <c r="P6" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="Q6" s="36" t="s">
+      <c r="Q6" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="R6" s="37" t="s">
+      <c r="R6" s="78" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:18" ht="21" x14ac:dyDescent="0.4">
       <c r="B7" s="38">
         <v>0.7</v>
       </c>
@@ -1846,32 +1880,32 @@
       <c r="J7" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="K7" s="54" t="s">
+      <c r="K7" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="L7" s="55" t="s">
+      <c r="L7" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="M7" s="55" t="s">
+      <c r="M7" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="N7" s="56" t="s">
+      <c r="N7" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="O7" s="35" t="s">
+      <c r="O7" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="P7" s="36" t="s">
+      <c r="P7" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="Q7" s="36" t="s">
+      <c r="Q7" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="R7" s="37" t="s">
+      <c r="R7" s="78" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:18" ht="21" x14ac:dyDescent="0.4">
       <c r="B8" s="38">
         <v>0.8</v>
       </c>
@@ -1899,32 +1933,32 @@
       <c r="J8" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="K8" s="54" t="s">
+      <c r="K8" s="70" t="s">
         <v>91</v>
       </c>
-      <c r="L8" s="55" t="s">
+      <c r="L8" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="M8" s="55" t="s">
+      <c r="M8" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="N8" s="56" t="s">
+      <c r="N8" s="72" t="s">
         <v>91</v>
       </c>
-      <c r="O8" s="35" t="s">
+      <c r="O8" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="P8" s="36" t="s">
+      <c r="P8" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="Q8" s="36" t="s">
+      <c r="Q8" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="R8" s="37" t="s">
+      <c r="R8" s="78" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="39">
         <v>0.9</v>
       </c>
@@ -1952,32 +1986,32 @@
       <c r="J9" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="K9" s="57" t="s">
+      <c r="K9" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="L9" s="58" t="s">
+      <c r="L9" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="M9" s="58" t="s">
+      <c r="M9" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="N9" s="59" t="s">
+      <c r="N9" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="O9" s="40" t="s">
+      <c r="O9" s="79" t="s">
         <v>97</v>
       </c>
-      <c r="P9" s="41" t="s">
+      <c r="P9" s="80" t="s">
         <v>97</v>
       </c>
-      <c r="Q9" s="41" t="s">
+      <c r="Q9" s="80" t="s">
         <v>97</v>
       </c>
-      <c r="R9" s="42" t="s">
+      <c r="R9" s="81" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:18" ht="21" x14ac:dyDescent="0.4">
       <c r="B10" s="52"/>
       <c r="C10" s="53"/>
       <c r="D10" s="53"/>
@@ -1996,10 +2030,10 @@
       <c r="Q10" s="53"/>
       <c r="R10" s="53"/>
     </row>
-    <row r="11" spans="2:18" ht="21" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:18" ht="21" x14ac:dyDescent="0.4">
       <c r="C11" s="48"/>
     </row>
-    <row r="12" spans="2:18" s="49" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:18" s="49" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="C12" s="50">
         <f>36/VALUE(TRIM(LEFT(C5, FIND("(", C5) - 1)))</f>
         <v>0.52173913043478259</v>
@@ -2061,7 +2095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:18" s="49" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:18" s="49" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B13" s="51"/>
       <c r="C13" s="50">
         <f>22/VALUE(TRIM(LEFT(C6, FIND("(", C6) - 1)))</f>
@@ -2123,7 +2157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:18" s="49" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:18" s="49" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B14" s="51"/>
       <c r="C14" s="50">
         <f>11/VALUE(TRIM(LEFT(C7, FIND("(", C7) - 1)))</f>
@@ -2185,7 +2219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:18" s="49" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:18" s="49" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B15" s="51"/>
       <c r="C15" s="50">
         <f>2/VALUE(TRIM(LEFT(C8, FIND("(", C8) - 1)))</f>
@@ -2245,7 +2279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:18" s="49" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:18" s="49" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B16" s="51"/>
       <c r="C16" s="50">
         <f>0/VALUE(TRIM(LEFT(C9, FIND("(", C9) - 1)))</f>
@@ -2302,377 +2336,377 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:18" s="49" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:18" s="49" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B17" s="51"/>
       <c r="C17" s="51"/>
       <c r="G17" s="51"/>
       <c r="K17" s="51"/>
       <c r="O17" s="51"/>
     </row>
-    <row r="20" spans="2:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="2:18" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B21" s="25"/>
-      <c r="C21" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="76"/>
-      <c r="E21" s="76"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="76"/>
-      <c r="H21" s="76"/>
-      <c r="I21" s="76"/>
-      <c r="J21" s="76"/>
-      <c r="K21" s="76"/>
-      <c r="L21" s="76"/>
-      <c r="M21" s="76"/>
-      <c r="N21" s="76"/>
-      <c r="O21" s="76"/>
-      <c r="P21" s="76"/>
-      <c r="Q21" s="76"/>
-      <c r="R21" s="77"/>
-    </row>
-    <row r="22" spans="2:18" ht="42" x14ac:dyDescent="0.35">
-      <c r="B22" s="60" t="s">
+      <c r="C21" s="82" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="83"/>
+      <c r="K21" s="83"/>
+      <c r="L21" s="83"/>
+      <c r="M21" s="83"/>
+      <c r="N21" s="83"/>
+      <c r="O21" s="83"/>
+      <c r="P21" s="83"/>
+      <c r="Q21" s="83"/>
+      <c r="R21" s="84"/>
+    </row>
+    <row r="22" spans="2:18" ht="42" x14ac:dyDescent="0.4">
+      <c r="B22" s="54" t="s">
         <v>175</v>
       </c>
-      <c r="C22" s="61">
+      <c r="C22" s="55">
         <v>2017</v>
       </c>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="61">
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="55">
         <v>2023</v>
       </c>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="63"/>
-      <c r="K22" s="61">
+      <c r="H22" s="56"/>
+      <c r="I22" s="56"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="55">
         <v>2024</v>
       </c>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="61" t="s">
+      <c r="L22" s="58"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="59"/>
+      <c r="O22" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="64"/>
-      <c r="R22" s="65"/>
-    </row>
-    <row r="23" spans="2:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="B23" s="66"/>
-      <c r="C23" s="67" t="s">
+      <c r="P22" s="58"/>
+      <c r="Q22" s="58"/>
+      <c r="R22" s="59"/>
+    </row>
+    <row r="23" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B23" s="60"/>
+      <c r="C23" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="D23" s="68" t="s">
+      <c r="D23" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="68" t="s">
+      <c r="E23" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="F23" s="69" t="s">
+      <c r="F23" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="G23" s="67" t="s">
+      <c r="G23" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="H23" s="68" t="s">
+      <c r="H23" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="I23" s="68" t="s">
+      <c r="I23" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="J23" s="69" t="s">
+      <c r="J23" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="K23" s="67" t="s">
+      <c r="K23" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="L23" s="68" t="s">
+      <c r="L23" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="M23" s="68" t="s">
+      <c r="M23" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="N23" s="69" t="s">
+      <c r="N23" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="O23" s="67" t="s">
+      <c r="O23" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="P23" s="68" t="s">
+      <c r="P23" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="Q23" s="68" t="s">
+      <c r="Q23" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="R23" s="69" t="s">
+      <c r="R23" s="63" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="2:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="B24" s="70">
+    <row r="24" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B24" s="64">
         <v>0.5</v>
       </c>
-      <c r="C24" s="67" t="s">
+      <c r="C24" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="D24" s="68" t="s">
+      <c r="D24" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="68" t="s">
+      <c r="E24" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="F24" s="69" t="s">
+      <c r="F24" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="G24" s="67" t="s">
+      <c r="G24" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="H24" s="68" t="s">
+      <c r="H24" s="62" t="s">
         <v>152</v>
       </c>
-      <c r="I24" s="68" t="s">
+      <c r="I24" s="62" t="s">
         <v>156</v>
       </c>
-      <c r="J24" s="69" t="s">
+      <c r="J24" s="63" t="s">
         <v>141</v>
       </c>
-      <c r="K24" s="67" t="s">
+      <c r="K24" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="L24" s="68" t="s">
+      <c r="L24" s="62" t="s">
         <v>162</v>
       </c>
-      <c r="M24" s="68" t="s">
+      <c r="M24" s="62" t="s">
         <v>163</v>
       </c>
-      <c r="N24" s="69" t="s">
+      <c r="N24" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="O24" s="67" t="s">
+      <c r="O24" s="61" t="s">
         <v>164</v>
       </c>
-      <c r="P24" s="68" t="s">
+      <c r="P24" s="62" t="s">
         <v>168</v>
       </c>
-      <c r="Q24" s="68" t="s">
+      <c r="Q24" s="62" t="s">
         <v>165</v>
       </c>
-      <c r="R24" s="69" t="s">
+      <c r="R24" s="63" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="25" spans="2:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="B25" s="70">
+    <row r="25" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B25" s="64">
         <v>0.6</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="68" t="s">
+      <c r="D25" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="E25" s="68" t="s">
+      <c r="E25" s="62" t="s">
         <v>131</v>
       </c>
-      <c r="F25" s="69" t="s">
+      <c r="F25" s="63" t="s">
         <v>135</v>
       </c>
-      <c r="G25" s="67" t="s">
+      <c r="G25" s="61" t="s">
         <v>149</v>
       </c>
-      <c r="H25" s="68" t="s">
+      <c r="H25" s="62" t="s">
         <v>153</v>
       </c>
-      <c r="I25" s="68" t="s">
+      <c r="I25" s="62" t="s">
         <v>157</v>
       </c>
-      <c r="J25" s="69" t="s">
+      <c r="J25" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="K25" s="67" t="s">
+      <c r="K25" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="L25" s="68" t="s">
+      <c r="L25" s="62" t="s">
         <v>142</v>
       </c>
-      <c r="M25" s="68" t="s">
+      <c r="M25" s="62" t="s">
         <v>160</v>
       </c>
-      <c r="N25" s="69" t="s">
+      <c r="N25" s="63" t="s">
         <v>142</v>
       </c>
-      <c r="O25" s="67" t="s">
+      <c r="O25" s="61" t="s">
         <v>165</v>
       </c>
-      <c r="P25" s="68" t="s">
+      <c r="P25" s="62" t="s">
         <v>169</v>
       </c>
-      <c r="Q25" s="68" t="s">
+      <c r="Q25" s="62" t="s">
         <v>172</v>
       </c>
-      <c r="R25" s="69" t="s">
+      <c r="R25" s="63" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="2:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="B26" s="70">
+    <row r="26" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B26" s="64">
         <v>0.7</v>
       </c>
-      <c r="C26" s="67" t="s">
+      <c r="C26" s="61" t="s">
         <v>125</v>
       </c>
-      <c r="D26" s="68" t="s">
+      <c r="D26" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="E26" s="68" t="s">
+      <c r="E26" s="62" t="s">
         <v>132</v>
       </c>
-      <c r="F26" s="69" t="s">
+      <c r="F26" s="63" t="s">
         <v>136</v>
       </c>
-      <c r="G26" s="67" t="s">
+      <c r="G26" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="H26" s="68" t="s">
+      <c r="H26" s="62" t="s">
         <v>154</v>
       </c>
-      <c r="I26" s="68" t="s">
+      <c r="I26" s="62" t="s">
         <v>158</v>
       </c>
-      <c r="J26" s="69" t="s">
+      <c r="J26" s="63" t="s">
         <v>139</v>
       </c>
-      <c r="K26" s="67" t="s">
+      <c r="K26" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="L26" s="68" t="s">
+      <c r="L26" s="62" t="s">
         <v>139</v>
       </c>
-      <c r="M26" s="68" t="s">
+      <c r="M26" s="62" t="s">
         <v>161</v>
       </c>
-      <c r="N26" s="69" t="s">
+      <c r="N26" s="63" t="s">
         <v>139</v>
       </c>
-      <c r="O26" s="67" t="s">
+      <c r="O26" s="61" t="s">
         <v>166</v>
       </c>
-      <c r="P26" s="68" t="s">
+      <c r="P26" s="62" t="s">
         <v>170</v>
       </c>
-      <c r="Q26" s="68" t="s">
+      <c r="Q26" s="62" t="s">
         <v>173</v>
       </c>
-      <c r="R26" s="69" t="s">
+      <c r="R26" s="63" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="2:18" ht="21" x14ac:dyDescent="0.35">
-      <c r="B27" s="70">
+    <row r="27" spans="2:18" ht="21" x14ac:dyDescent="0.4">
+      <c r="B27" s="64">
         <v>0.8</v>
       </c>
-      <c r="C27" s="67" t="s">
+      <c r="C27" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="68" t="s">
+      <c r="D27" s="62" t="s">
         <v>134</v>
       </c>
-      <c r="E27" s="68" t="s">
+      <c r="E27" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="F27" s="69" t="s">
+      <c r="F27" s="63" t="s">
         <v>134</v>
       </c>
-      <c r="G27" s="67" t="s">
+      <c r="G27" s="61" t="s">
         <v>151</v>
       </c>
-      <c r="H27" s="68" t="s">
+      <c r="H27" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="I27" s="68" t="s">
+      <c r="I27" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="J27" s="69" t="s">
+      <c r="J27" s="63" t="s">
         <v>138</v>
       </c>
-      <c r="K27" s="67" t="s">
+      <c r="K27" s="61" t="s">
         <v>133</v>
       </c>
-      <c r="L27" s="68" t="s">
+      <c r="L27" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="M27" s="68" t="s">
+      <c r="M27" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="N27" s="69" t="s">
+      <c r="N27" s="63" t="s">
         <v>133</v>
       </c>
-      <c r="O27" s="67" t="s">
+      <c r="O27" s="61" t="s">
         <v>167</v>
       </c>
-      <c r="P27" s="68" t="s">
+      <c r="P27" s="62" t="s">
         <v>171</v>
       </c>
-      <c r="Q27" s="68" t="s">
+      <c r="Q27" s="62" t="s">
         <v>174</v>
       </c>
-      <c r="R27" s="69" t="s">
+      <c r="R27" s="63" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="28" spans="2:18" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="71">
+    <row r="28" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B28" s="65">
         <v>0.9</v>
       </c>
-      <c r="C28" s="72" t="s">
+      <c r="C28" s="66" t="s">
         <v>133</v>
       </c>
-      <c r="D28" s="73" t="s">
+      <c r="D28" s="67" t="s">
         <v>133</v>
       </c>
-      <c r="E28" s="73" t="s">
+      <c r="E28" s="67" t="s">
         <v>133</v>
       </c>
-      <c r="F28" s="74" t="s">
+      <c r="F28" s="68" t="s">
         <v>133</v>
       </c>
-      <c r="G28" s="72" t="s">
+      <c r="G28" s="66" t="s">
         <v>137</v>
       </c>
-      <c r="H28" s="73" t="s">
+      <c r="H28" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="I28" s="73" t="s">
+      <c r="I28" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="J28" s="74" t="s">
+      <c r="J28" s="68" t="s">
         <v>137</v>
       </c>
-      <c r="K28" s="72" t="s">
+      <c r="K28" s="66" t="s">
         <v>137</v>
       </c>
-      <c r="L28" s="73" t="s">
+      <c r="L28" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="M28" s="73" t="s">
+      <c r="M28" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="N28" s="74" t="s">
+      <c r="N28" s="68" t="s">
         <v>137</v>
       </c>
-      <c r="O28" s="72" t="s">
+      <c r="O28" s="66" t="s">
         <v>143</v>
       </c>
-      <c r="P28" s="73" t="s">
+      <c r="P28" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="Q28" s="73" t="s">
+      <c r="Q28" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="R28" s="74" t="s">
+      <c r="R28" s="68" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2688,15 +2722,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:O18"/>
-  <sheetFormatPr defaultColWidth="14.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="35.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="35.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="83.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
@@ -2734,7 +2768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:15" ht="68.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" ht="62.4" x14ac:dyDescent="0.3">
       <c r="B3" s="11">
         <v>2010</v>
       </c>
@@ -2770,7 +2804,7 @@
       </c>
       <c r="O3" s="44"/>
     </row>
-    <row r="4" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="11">
         <v>2011</v>
       </c>
@@ -2804,7 +2838,7 @@
       <c r="L4" s="13"/>
       <c r="O4" s="44"/>
     </row>
-    <row r="5" spans="2:15" ht="57" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" ht="52.2" x14ac:dyDescent="0.3">
       <c r="B5" s="11">
         <v>2012</v>
       </c>
@@ -2840,7 +2874,7 @@
       </c>
       <c r="O5" s="44"/>
     </row>
-    <row r="6" spans="2:15" ht="57" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" ht="52.2" x14ac:dyDescent="0.3">
       <c r="B6" s="11">
         <v>2013</v>
       </c>
@@ -2876,7 +2910,7 @@
       </c>
       <c r="O6" s="44"/>
     </row>
-    <row r="7" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="11">
         <v>2015</v>
       </c>
@@ -2910,7 +2944,7 @@
       <c r="L7" s="13"/>
       <c r="O7" s="44"/>
     </row>
-    <row r="8" spans="2:15" ht="57" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" ht="52.2" x14ac:dyDescent="0.3">
       <c r="B8" s="11">
         <v>2016</v>
       </c>
@@ -2946,7 +2980,7 @@
       </c>
       <c r="O8" s="44"/>
     </row>
-    <row r="9" spans="2:15" ht="109.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11">
         <v>2017</v>
       </c>
@@ -2982,7 +3016,7 @@
       </c>
       <c r="O9" s="44"/>
     </row>
-    <row r="10" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="11">
         <v>2018</v>
       </c>
@@ -3016,7 +3050,7 @@
       <c r="L10" s="13"/>
       <c r="O10" s="44"/>
     </row>
-    <row r="11" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="11">
         <v>2019</v>
       </c>
@@ -3050,7 +3084,7 @@
       <c r="L11" s="13"/>
       <c r="O11" s="44"/>
     </row>
-    <row r="12" spans="2:15" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="11">
         <v>2020</v>
       </c>
@@ -3086,7 +3120,7 @@
       </c>
       <c r="O12" s="44"/>
     </row>
-    <row r="13" spans="2:15" ht="68.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" ht="62.4" x14ac:dyDescent="0.3">
       <c r="B13" s="11">
         <v>2021</v>
       </c>
@@ -3122,7 +3156,7 @@
       </c>
       <c r="O13" s="44"/>
     </row>
-    <row r="14" spans="2:15" ht="79.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" ht="72.599999999999994" x14ac:dyDescent="0.3">
       <c r="B14" s="11">
         <v>2023</v>
       </c>
@@ -3141,7 +3175,7 @@
       <c r="G14" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="H14" s="79">
+      <c r="H14" s="69">
         <f>733+435</f>
         <v>1168</v>
       </c>
@@ -3159,7 +3193,7 @@
       </c>
       <c r="O14" s="44"/>
     </row>
-    <row r="15" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="11">
         <v>2024</v>
       </c>
@@ -3193,7 +3227,7 @@
       <c r="L15" s="13"/>
       <c r="O15" s="44"/>
     </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J18" t="s">
         <v>114</v>
       </c>
@@ -3209,16 +3243,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C3CA73-E650-4EB7-93C1-D459BAC41A38}">
   <dimension ref="A3:L31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="12" width="10.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" customWidth="1"/>
+    <col min="6" max="12" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="17" t="s">
         <v>0</v>
       </c>
@@ -3246,7 +3280,7 @@
       </c>
       <c r="L3" s="14"/>
     </row>
-    <row r="4" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B4" s="16">
         <v>2017</v>
       </c>
@@ -3279,7 +3313,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="16">
         <v>2023</v>
       </c>
@@ -3290,14 +3324,14 @@
         <v>321</v>
       </c>
       <c r="E5" s="16">
-        <f t="shared" ref="E5:E9" si="0">ROUND((C5-D5)/C5, 2)</f>
+        <f>ROUND((C5-D5)/C5, 2)</f>
         <v>0.17</v>
       </c>
       <c r="F5" s="16">
         <v>67</v>
       </c>
       <c r="G5" s="16">
-        <f t="shared" ref="G5:G9" si="1">ROUND((D5-F5)/D5, 2)</f>
+        <f>ROUND((D5-F5)/D5, 2)</f>
         <v>0.79</v>
       </c>
       <c r="H5" s="16">
@@ -3312,7 +3346,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="18">
         <v>2024</v>
       </c>
@@ -3323,14 +3357,14 @@
         <v>87</v>
       </c>
       <c r="E6" s="18">
-        <f t="shared" si="0"/>
+        <f>ROUND((C6-D6)/C6, 2)</f>
         <v>0.28999999999999998</v>
       </c>
       <c r="F6" s="18">
         <v>35</v>
       </c>
       <c r="G6" s="18">
-        <f t="shared" si="1"/>
+        <f>ROUND((D6-F6)/D6, 2)</f>
         <v>0.6</v>
       </c>
       <c r="H6" s="18">
@@ -3345,8 +3379,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>29</v>
       </c>
@@ -3359,7 +3393,7 @@
         <v>856</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
+        <f>ROUND((C9-D9)/C9, 2)</f>
         <v>0.2</v>
       </c>
       <c r="F9">
@@ -3367,11 +3401,11 @@
         <v>212</v>
       </c>
       <c r="G9">
-        <f t="shared" si="1"/>
+        <f>ROUND((D9-F9)/D9, 2)</f>
         <v>0.75</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>28</v>
       </c>
@@ -3380,17 +3414,17 @@
         <v>209</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>32</v>
       </c>
@@ -3404,7 +3438,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>555</v>
       </c>
@@ -3419,7 +3453,7 @@
         <v>0.80180180180180183</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>388</v>
       </c>
@@ -3430,11 +3464,11 @@
         <v>14</v>
       </c>
       <c r="E20" s="19">
-        <f t="shared" ref="E20:E21" si="2">(B20-C20)/B20</f>
+        <f>(B20-C20)/B20</f>
         <v>0.82731958762886593</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>122</v>
       </c>
@@ -3445,11 +3479,11 @@
         <v>10</v>
       </c>
       <c r="E21" s="19">
-        <f t="shared" si="2"/>
+        <f>(B21-C21)/B21</f>
         <v>0.71311475409836067</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
         <v>32</v>
       </c>
@@ -3467,7 +3501,7 @@
       </c>
       <c r="E22" s="20"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -3476,7 +3510,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -3485,7 +3519,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
         <v>38</v>
       </c>
@@ -3494,7 +3528,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="20" t="s">
         <v>39</v>
       </c>
@@ -3503,7 +3537,7 @@
         <v>0.8037558685446009</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="20" t="s">
         <v>40</v>
       </c>
@@ -3512,7 +3546,7 @@
         <v>0.78074538117634285</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>41</v>
       </c>
@@ -3530,21 +3564,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC43C8DF-330E-4085-938E-0299F38AFB9F}">
   <dimension ref="B3:G13"/>
-  <sheetFormatPr defaultColWidth="21.5703125" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.5546875" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-    </row>
-    <row r="4" spans="2:7" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+    </row>
+    <row r="4" spans="2:7" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="3"/>
       <c r="C4" s="6" t="s">
         <v>19</v>
@@ -3556,7 +3590,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B5" s="10">
         <v>2017</v>
       </c>
@@ -3578,7 +3612,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5">
         <v>2023</v>
       </c>
@@ -3592,15 +3626,15 @@
         <v>5</v>
       </c>
       <c r="F6">
-        <f t="shared" ref="F6:F7" si="0">C6+D6+E6</f>
+        <f>C6+D6+E6</f>
         <v>388</v>
       </c>
       <c r="G6">
-        <f t="shared" ref="G6:G7" si="1">D6+E6</f>
+        <f>D6+E6</f>
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5">
         <v>2024</v>
       </c>
@@ -3614,45 +3648,45 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <f t="shared" si="0"/>
+        <f>C7+D7+E7</f>
         <v>132</v>
       </c>
       <c r="G7">
-        <f t="shared" si="1"/>
+        <f>D7+E7</f>
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
